--- a/VerveStacks_FRA_grids_kan25/SuppXLS/Scen_TSParameters_ts_60.xlsx
+++ b/VerveStacks_FRA_grids_kan25/SuppXLS/Scen_TSParameters_ts_60.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_FRA_grids_kan25\SuppXLS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_FRA_grids_kan25\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B3BD4E5F-6AEC-4A17-A9E1-28AC6617C1D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8DC4D69-B78E-4D11-97C2-F276656B5AB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -903,12 +903,6 @@
     <t>S01aH09,S03aH08,S03aH10,S06aH08,S06aH09,S01aH02,S05aH10,S04aH02,S02aH09,S04aH09,S05aH01,S01aH10,S03aH02,S02aH02,S04aH10,S06aH10,S05aH08,S02aH01,S02aH10,S05aH02,S03aH09,S05aH09,S01aH01,S04aH01,S06aH02,S03aH01,S01aH08,S02aH08,S04aH08,S06aH01</t>
   </si>
   <si>
-    <t>elc_buildings</t>
-  </si>
-  <si>
-    <t>elc_industry</t>
-  </si>
-  <si>
     <t>com_pkflx</t>
   </si>
   <si>
@@ -922,6 +916,12 @@
   </si>
   <si>
     <t>hydro</t>
+  </si>
+  <si>
+    <t>*[_]buildings</t>
+  </si>
+  <si>
+    <t>*[_]industry</t>
   </si>
 </sst>
 </file>
@@ -90060,6 +90060,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7CCA5E0-2F8D-4862-8873-589F84DB6C7F}">
   <dimension ref="A9:S184"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="8" max="8" width="12.1328125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="9" spans="1:19" x14ac:dyDescent="0.45">
       <c r="C9" t="str">
@@ -90067,8 +90070,8 @@
         <v>~TFM_DINS-AT</v>
       </c>
       <c r="H9" t="str">
-        <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
-        <v>~TFM_DINS-AT</v>
+        <f>IF(A11="x","DeActivated","~TFM_INS-AT:cset_set=DEM")</f>
+        <v>~TFM_INS-AT:cset_set=DEM</v>
       </c>
       <c r="L9" t="str">
         <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
@@ -90111,19 +90114,19 @@
         <v>57</v>
       </c>
       <c r="N10" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="P10" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="Q10" t="s">
         <v>57</v>
       </c>
       <c r="R10" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="S10" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.45">
@@ -90144,7 +90147,7 @@
         <v>281</v>
       </c>
       <c r="H11" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I11" t="s">
         <v>61</v>
@@ -90171,7 +90174,7 @@
         <v>0.32884999999999998</v>
       </c>
       <c r="S11" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.45">
@@ -90188,7 +90191,7 @@
         <v>281</v>
       </c>
       <c r="H12" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I12" t="s">
         <v>63</v>
@@ -90215,7 +90218,7 @@
         <v>0.32379999999999998</v>
       </c>
       <c r="S12" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.45">
@@ -90232,7 +90235,7 @@
         <v>281</v>
       </c>
       <c r="H13" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I13" t="s">
         <v>64</v>
@@ -90259,7 +90262,7 @@
         <v>0.33195000000000002</v>
       </c>
       <c r="S13" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.45">
@@ -90276,7 +90279,7 @@
         <v>281</v>
       </c>
       <c r="H14" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I14" t="s">
         <v>65</v>
@@ -90303,7 +90306,7 @@
         <v>0.20910000000000001</v>
       </c>
       <c r="S14" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.45">
@@ -90320,7 +90323,7 @@
         <v>281</v>
       </c>
       <c r="H15" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I15" t="s">
         <v>66</v>
@@ -90347,7 +90350,7 @@
         <v>0.20760000000000001</v>
       </c>
       <c r="S15" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.45">
@@ -90364,7 +90367,7 @@
         <v>281</v>
       </c>
       <c r="H16" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I16" t="s">
         <v>67</v>
@@ -90391,7 +90394,7 @@
         <v>0.26144999999999996</v>
       </c>
       <c r="S16" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="17" spans="3:19" x14ac:dyDescent="0.45">
@@ -90408,7 +90411,7 @@
         <v>281</v>
       </c>
       <c r="H17" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I17" t="s">
         <v>68</v>
@@ -90435,7 +90438,7 @@
         <v>0.38249999999999995</v>
       </c>
       <c r="S17" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="18" spans="3:19" x14ac:dyDescent="0.45">
@@ -90452,7 +90455,7 @@
         <v>281</v>
       </c>
       <c r="H18" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I18" t="s">
         <v>69</v>
@@ -90479,7 +90482,7 @@
         <v>0.25664999999999999</v>
       </c>
       <c r="S18" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="19" spans="3:19" x14ac:dyDescent="0.45">
@@ -90496,7 +90499,7 @@
         <v>281</v>
       </c>
       <c r="H19" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I19" t="s">
         <v>70</v>
@@ -90523,7 +90526,7 @@
         <v>0.32330000000000003</v>
       </c>
       <c r="S19" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="20" spans="3:19" x14ac:dyDescent="0.45">
@@ -90540,7 +90543,7 @@
         <v>281</v>
       </c>
       <c r="H20" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I20" t="s">
         <v>71</v>
@@ -90567,7 +90570,7 @@
         <v>0.251</v>
       </c>
       <c r="S20" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="21" spans="3:19" x14ac:dyDescent="0.45">
@@ -90584,7 +90587,7 @@
         <v>281</v>
       </c>
       <c r="H21" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I21" t="s">
         <v>72</v>
@@ -90611,7 +90614,7 @@
         <v>0.16105</v>
       </c>
       <c r="S21" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="22" spans="3:19" x14ac:dyDescent="0.45">
@@ -90628,7 +90631,7 @@
         <v>281</v>
       </c>
       <c r="H22" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I22" t="s">
         <v>73</v>
@@ -90655,7 +90658,7 @@
         <v>0.21995000000000001</v>
       </c>
       <c r="S22" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="23" spans="3:19" x14ac:dyDescent="0.45">
@@ -90672,7 +90675,7 @@
         <v>281</v>
       </c>
       <c r="H23" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I23" t="s">
         <v>74</v>
@@ -90699,7 +90702,7 @@
         <v>0.25940000000000002</v>
       </c>
       <c r="S23" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="24" spans="3:19" x14ac:dyDescent="0.45">
@@ -90716,7 +90719,7 @@
         <v>281</v>
       </c>
       <c r="H24" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I24" t="s">
         <v>75</v>
@@ -90743,7 +90746,7 @@
         <v>0.23335</v>
       </c>
       <c r="S24" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="25" spans="3:19" x14ac:dyDescent="0.45">
@@ -90760,7 +90763,7 @@
         <v>281</v>
       </c>
       <c r="H25" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I25" t="s">
         <v>76</v>
@@ -90787,7 +90790,7 @@
         <v>0.22620000000000001</v>
       </c>
       <c r="S25" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="3:19" x14ac:dyDescent="0.45">
@@ -90804,7 +90807,7 @@
         <v>281</v>
       </c>
       <c r="H26" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I26" t="s">
         <v>77</v>
@@ -90831,7 +90834,7 @@
         <v>0.15055000000000002</v>
       </c>
       <c r="S26" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="3:19" x14ac:dyDescent="0.45">
@@ -90848,7 +90851,7 @@
         <v>281</v>
       </c>
       <c r="H27" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I27" t="s">
         <v>78</v>
@@ -90875,7 +90878,7 @@
         <v>0.13195000000000001</v>
       </c>
       <c r="S27" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="28" spans="3:19" x14ac:dyDescent="0.45">
@@ -90892,7 +90895,7 @@
         <v>281</v>
       </c>
       <c r="H28" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I28" t="s">
         <v>79</v>
@@ -90919,7 +90922,7 @@
         <v>0.21455000000000002</v>
       </c>
       <c r="S28" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="3:19" x14ac:dyDescent="0.45">
@@ -90936,7 +90939,7 @@
         <v>281</v>
       </c>
       <c r="H29" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I29" t="s">
         <v>80</v>
@@ -90963,7 +90966,7 @@
         <v>0.34404999999999997</v>
       </c>
       <c r="S29" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="30" spans="3:19" x14ac:dyDescent="0.45">
@@ -90980,7 +90983,7 @@
         <v>281</v>
       </c>
       <c r="H30" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I30" t="s">
         <v>81</v>
@@ -91007,7 +91010,7 @@
         <v>0.26339999999999997</v>
       </c>
       <c r="S30" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="31" spans="3:19" x14ac:dyDescent="0.45">
@@ -91024,7 +91027,7 @@
         <v>281</v>
       </c>
       <c r="H31" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I31" t="s">
         <v>82</v>
@@ -91051,7 +91054,7 @@
         <v>0.3</v>
       </c>
       <c r="S31" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="32" spans="3:19" x14ac:dyDescent="0.45">
@@ -91068,7 +91071,7 @@
         <v>281</v>
       </c>
       <c r="H32" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I32" t="s">
         <v>83</v>
@@ -91095,7 +91098,7 @@
         <v>0.192</v>
       </c>
       <c r="S32" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="33" spans="3:19" x14ac:dyDescent="0.45">
@@ -91112,7 +91115,7 @@
         <v>281</v>
       </c>
       <c r="H33" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I33" t="s">
         <v>84</v>
@@ -91139,7 +91142,7 @@
         <v>0.18359999999999999</v>
       </c>
       <c r="S33" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="34" spans="3:19" x14ac:dyDescent="0.45">
@@ -91156,7 +91159,7 @@
         <v>281</v>
       </c>
       <c r="H34" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I34" t="s">
         <v>85</v>
@@ -91183,7 +91186,7 @@
         <v>0.22505</v>
       </c>
       <c r="S34" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="35" spans="3:19" x14ac:dyDescent="0.45">
@@ -91200,7 +91203,7 @@
         <v>281</v>
       </c>
       <c r="H35" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I35" t="s">
         <v>86</v>
@@ -91227,7 +91230,7 @@
         <v>0.3337</v>
       </c>
       <c r="S35" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="36" spans="3:19" x14ac:dyDescent="0.45">
@@ -91244,7 +91247,7 @@
         <v>281</v>
       </c>
       <c r="H36" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I36" t="s">
         <v>87</v>
@@ -91271,7 +91274,7 @@
         <v>0.25495000000000001</v>
       </c>
       <c r="S36" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="37" spans="3:19" x14ac:dyDescent="0.45">
@@ -91288,7 +91291,7 @@
         <v>281</v>
       </c>
       <c r="H37" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I37" t="s">
         <v>88</v>
@@ -91315,7 +91318,7 @@
         <v>0.26024999999999998</v>
       </c>
       <c r="S37" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="38" spans="3:19" x14ac:dyDescent="0.45">
@@ -91332,7 +91335,7 @@
         <v>281</v>
       </c>
       <c r="H38" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I38" t="s">
         <v>89</v>
@@ -91359,7 +91362,7 @@
         <v>0.2064</v>
       </c>
       <c r="S38" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="39" spans="3:19" x14ac:dyDescent="0.45">
@@ -91376,7 +91379,7 @@
         <v>281</v>
       </c>
       <c r="H39" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I39" t="s">
         <v>90</v>
@@ -91403,7 +91406,7 @@
         <v>0.18104999999999999</v>
       </c>
       <c r="S39" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="40" spans="3:19" x14ac:dyDescent="0.45">
@@ -91420,7 +91423,7 @@
         <v>281</v>
       </c>
       <c r="H40" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I40" t="s">
         <v>91</v>
@@ -91447,7 +91450,7 @@
         <v>0.23249999999999998</v>
       </c>
       <c r="S40" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="41" spans="3:19" x14ac:dyDescent="0.45">
@@ -91464,7 +91467,7 @@
         <v>281</v>
       </c>
       <c r="H41" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I41" t="s">
         <v>92</v>
@@ -91491,7 +91494,7 @@
         <v>0.32094999999999996</v>
       </c>
       <c r="S41" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="42" spans="3:19" x14ac:dyDescent="0.45">
@@ -91508,7 +91511,7 @@
         <v>281</v>
       </c>
       <c r="H42" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I42" t="s">
         <v>93</v>
@@ -91535,7 +91538,7 @@
         <v>0.33640000000000003</v>
       </c>
       <c r="S42" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="43" spans="3:19" x14ac:dyDescent="0.45">
@@ -91552,7 +91555,7 @@
         <v>281</v>
       </c>
       <c r="H43" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I43" t="s">
         <v>94</v>
@@ -91579,7 +91582,7 @@
         <v>0.3276</v>
       </c>
       <c r="S43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="44" spans="3:19" x14ac:dyDescent="0.45">
@@ -91596,7 +91599,7 @@
         <v>281</v>
       </c>
       <c r="H44" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I44" t="s">
         <v>95</v>
@@ -91623,7 +91626,7 @@
         <v>0.18459999999999999</v>
       </c>
       <c r="S44" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="45" spans="3:19" x14ac:dyDescent="0.45">
@@ -91640,7 +91643,7 @@
         <v>281</v>
       </c>
       <c r="H45" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I45" t="s">
         <v>96</v>
@@ -91667,7 +91670,7 @@
         <v>0.20365</v>
       </c>
       <c r="S45" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="46" spans="3:19" x14ac:dyDescent="0.45">
@@ -91684,7 +91687,7 @@
         <v>281</v>
       </c>
       <c r="H46" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I46" t="s">
         <v>97</v>
@@ -91711,7 +91714,7 @@
         <v>0.23815000000000003</v>
       </c>
       <c r="S46" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="47" spans="3:19" x14ac:dyDescent="0.45">
@@ -91728,7 +91731,7 @@
         <v>281</v>
       </c>
       <c r="H47" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I47" t="s">
         <v>98</v>
@@ -91755,7 +91758,7 @@
         <v>0.3876</v>
       </c>
       <c r="S47" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="48" spans="3:19" x14ac:dyDescent="0.45">
@@ -91772,7 +91775,7 @@
         <v>281</v>
       </c>
       <c r="H48" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I48" t="s">
         <v>99</v>
@@ -91799,7 +91802,7 @@
         <v>0.33899999999999997</v>
       </c>
       <c r="S48" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="49" spans="3:19" x14ac:dyDescent="0.45">
@@ -91816,7 +91819,7 @@
         <v>281</v>
       </c>
       <c r="H49" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I49" t="s">
         <v>100</v>
@@ -91843,7 +91846,7 @@
         <v>0.35389999999999999</v>
       </c>
       <c r="S49" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="50" spans="3:19" x14ac:dyDescent="0.45">
@@ -91860,7 +91863,7 @@
         <v>281</v>
       </c>
       <c r="H50" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I50" t="s">
         <v>101</v>
@@ -91887,7 +91890,7 @@
         <v>0.21375</v>
       </c>
       <c r="S50" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="51" spans="3:19" x14ac:dyDescent="0.45">
@@ -91904,7 +91907,7 @@
         <v>281</v>
       </c>
       <c r="H51" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I51" t="s">
         <v>102</v>
@@ -91931,7 +91934,7 @@
         <v>0.18010000000000001</v>
       </c>
       <c r="S51" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="52" spans="3:19" x14ac:dyDescent="0.45">
@@ -91948,7 +91951,7 @@
         <v>281</v>
       </c>
       <c r="H52" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I52" t="s">
         <v>103</v>
@@ -91975,7 +91978,7 @@
         <v>0.26650000000000001</v>
       </c>
       <c r="S52" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="53" spans="3:19" x14ac:dyDescent="0.45">
@@ -91992,7 +91995,7 @@
         <v>281</v>
       </c>
       <c r="H53" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I53" t="s">
         <v>104</v>
@@ -92019,7 +92022,7 @@
         <v>0.34970000000000001</v>
       </c>
       <c r="S53" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="54" spans="3:19" x14ac:dyDescent="0.45">
@@ -92036,7 +92039,7 @@
         <v>281</v>
       </c>
       <c r="H54" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I54" t="s">
         <v>105</v>
@@ -92063,7 +92066,7 @@
         <v>0.32765</v>
       </c>
       <c r="S54" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="55" spans="3:19" x14ac:dyDescent="0.45">
@@ -92080,7 +92083,7 @@
         <v>281</v>
       </c>
       <c r="H55" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I55" t="s">
         <v>106</v>
@@ -92107,7 +92110,7 @@
         <v>0.36409999999999998</v>
       </c>
       <c r="S55" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="56" spans="3:19" x14ac:dyDescent="0.45">
@@ -92124,7 +92127,7 @@
         <v>281</v>
       </c>
       <c r="H56" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I56" t="s">
         <v>107</v>
@@ -92151,7 +92154,7 @@
         <v>0.19919999999999999</v>
       </c>
       <c r="S56" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="57" spans="3:19" x14ac:dyDescent="0.45">
@@ -92168,7 +92171,7 @@
         <v>281</v>
       </c>
       <c r="H57" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I57" t="s">
         <v>108</v>
@@ -92195,7 +92198,7 @@
         <v>0.1653</v>
       </c>
       <c r="S57" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="58" spans="3:19" x14ac:dyDescent="0.45">
@@ -92212,7 +92215,7 @@
         <v>281</v>
       </c>
       <c r="H58" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I58" t="s">
         <v>109</v>
@@ -92239,7 +92242,7 @@
         <v>0.21804999999999999</v>
       </c>
       <c r="S58" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="59" spans="3:19" x14ac:dyDescent="0.45">
@@ -92256,7 +92259,7 @@
         <v>281</v>
       </c>
       <c r="H59" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I59" t="s">
         <v>110</v>
@@ -92283,7 +92286,7 @@
         <v>0.30020000000000002</v>
       </c>
       <c r="S59" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="60" spans="3:19" x14ac:dyDescent="0.45">
@@ -92300,7 +92303,7 @@
         <v>281</v>
       </c>
       <c r="H60" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I60" t="s">
         <v>111</v>
@@ -92327,7 +92330,7 @@
         <v>0.34819999999999995</v>
       </c>
       <c r="S60" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="61" spans="3:19" x14ac:dyDescent="0.45">
@@ -92344,7 +92347,7 @@
         <v>281</v>
       </c>
       <c r="H61" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I61" t="s">
         <v>112</v>
@@ -92371,7 +92374,7 @@
         <v>0.36664999999999998</v>
       </c>
       <c r="S61" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="62" spans="3:19" x14ac:dyDescent="0.45">
@@ -92388,7 +92391,7 @@
         <v>281</v>
       </c>
       <c r="H62" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I62" t="s">
         <v>113</v>
@@ -92415,7 +92418,7 @@
         <v>0.2026</v>
       </c>
       <c r="S62" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="63" spans="3:19" x14ac:dyDescent="0.45">
@@ -92432,7 +92435,7 @@
         <v>281</v>
       </c>
       <c r="H63" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I63" t="s">
         <v>114</v>
@@ -92459,7 +92462,7 @@
         <v>0.18235000000000001</v>
       </c>
       <c r="S63" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="64" spans="3:19" x14ac:dyDescent="0.45">
@@ -92476,7 +92479,7 @@
         <v>281</v>
       </c>
       <c r="H64" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I64" t="s">
         <v>115</v>
@@ -92503,7 +92506,7 @@
         <v>0.29704999999999998</v>
       </c>
       <c r="S64" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="65" spans="3:19" x14ac:dyDescent="0.45">
@@ -92520,7 +92523,7 @@
         <v>281</v>
       </c>
       <c r="H65" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I65" t="s">
         <v>116</v>
@@ -92547,7 +92550,7 @@
         <v>0.33479999999999999</v>
       </c>
       <c r="S65" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="66" spans="3:19" x14ac:dyDescent="0.45">
@@ -92564,7 +92567,7 @@
         <v>281</v>
       </c>
       <c r="H66" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I66" t="s">
         <v>117</v>
@@ -92591,7 +92594,7 @@
         <v>0.33210000000000001</v>
       </c>
       <c r="S66" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="67" spans="3:19" x14ac:dyDescent="0.45">
@@ -92608,7 +92611,7 @@
         <v>281</v>
       </c>
       <c r="H67" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I67" t="s">
         <v>118</v>
@@ -92635,7 +92638,7 @@
         <v>0.34714999999999996</v>
       </c>
       <c r="S67" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="68" spans="3:19" x14ac:dyDescent="0.45">
@@ -92652,7 +92655,7 @@
         <v>281</v>
       </c>
       <c r="H68" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I68" t="s">
         <v>119</v>
@@ -92679,7 +92682,7 @@
         <v>0.24829999999999999</v>
       </c>
       <c r="S68" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="69" spans="3:19" x14ac:dyDescent="0.45">
@@ -92696,7 +92699,7 @@
         <v>281</v>
       </c>
       <c r="H69" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I69" t="s">
         <v>120</v>
@@ -92723,7 +92726,7 @@
         <v>0.17255000000000001</v>
       </c>
       <c r="S69" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="70" spans="3:19" x14ac:dyDescent="0.45">
@@ -92740,7 +92743,7 @@
         <v>281</v>
       </c>
       <c r="H70" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I70" t="s">
         <v>121</v>
@@ -92767,12 +92770,12 @@
         <v>0.29925000000000002</v>
       </c>
       <c r="S70" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="71" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H71" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I71" t="s">
         <v>61</v>
@@ -92790,12 +92793,12 @@
         <v>0.30010000000000003</v>
       </c>
       <c r="S71" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="72" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H72" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I72" t="s">
         <v>63</v>
@@ -92813,12 +92816,12 @@
         <v>0.23294999999999999</v>
       </c>
       <c r="S72" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="73" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H73" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I73" t="s">
         <v>64</v>
@@ -92836,12 +92839,12 @@
         <v>0.28615000000000002</v>
       </c>
       <c r="S73" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="74" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H74" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I74" t="s">
         <v>65</v>
@@ -92859,12 +92862,12 @@
         <v>0.20265</v>
       </c>
       <c r="S74" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="75" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H75" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I75" t="s">
         <v>66</v>
@@ -92882,12 +92885,12 @@
         <v>0.152</v>
       </c>
       <c r="S75" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="76" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H76" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I76" t="s">
         <v>67</v>
@@ -92905,12 +92908,12 @@
         <v>0.24084999999999998</v>
       </c>
       <c r="S76" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="77" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H77" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I77" t="s">
         <v>68</v>
@@ -92928,12 +92931,12 @@
         <v>0.30495</v>
       </c>
       <c r="S77" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="78" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H78" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I78" t="s">
         <v>69</v>
@@ -92951,12 +92954,12 @@
         <v>0.33194999999999997</v>
       </c>
       <c r="S78" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="79" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H79" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I79" t="s">
         <v>70</v>
@@ -92974,12 +92977,12 @@
         <v>0.31174999999999997</v>
       </c>
       <c r="S79" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="80" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H80" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I80" t="s">
         <v>71</v>
@@ -92997,12 +93000,12 @@
         <v>0.24269999999999997</v>
       </c>
       <c r="S80" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="81" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H81" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I81" t="s">
         <v>72</v>
@@ -93020,12 +93023,12 @@
         <v>0.1401</v>
       </c>
       <c r="S81" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="82" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H82" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I82" t="s">
         <v>73</v>
@@ -93043,12 +93046,12 @@
         <v>0.26954999999999996</v>
       </c>
       <c r="S82" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="83" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H83" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I83" t="s">
         <v>74</v>
@@ -93066,12 +93069,12 @@
         <v>0.2893</v>
       </c>
       <c r="S83" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="84" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H84" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I84" t="s">
         <v>75</v>
@@ -93089,12 +93092,12 @@
         <v>0.25214999999999999</v>
       </c>
       <c r="S84" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="85" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H85" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I85" t="s">
         <v>76</v>
@@ -93112,12 +93115,12 @@
         <v>0.28079999999999999</v>
       </c>
       <c r="S85" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="86" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H86" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I86" t="s">
         <v>77</v>
@@ -93135,12 +93138,12 @@
         <v>0.2311</v>
       </c>
       <c r="S86" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="87" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H87" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I87" t="s">
         <v>78</v>
@@ -93158,12 +93161,12 @@
         <v>0.10925</v>
       </c>
       <c r="S87" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="88" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H88" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I88" t="s">
         <v>79</v>
@@ -93181,12 +93184,12 @@
         <v>0.24104999999999999</v>
       </c>
       <c r="S88" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="89" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H89" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I89" t="s">
         <v>80</v>
@@ -93204,12 +93207,12 @@
         <v>0.30325000000000002</v>
       </c>
       <c r="S89" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="90" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H90" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I90" t="s">
         <v>81</v>
@@ -93227,12 +93230,12 @@
         <v>0.34694999999999998</v>
       </c>
       <c r="S90" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="91" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H91" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I91" t="s">
         <v>82</v>
@@ -93250,12 +93253,12 @@
         <v>0.30105000000000004</v>
       </c>
       <c r="S91" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="92" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H92" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I92" t="s">
         <v>83</v>
@@ -93273,12 +93276,12 @@
         <v>0.23320000000000002</v>
       </c>
       <c r="S92" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="93" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H93" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I93" t="s">
         <v>84</v>
@@ -93296,12 +93299,12 @@
         <v>0.16464999999999999</v>
       </c>
       <c r="S93" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="94" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H94" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I94" t="s">
         <v>85</v>
@@ -93319,12 +93322,12 @@
         <v>0.2283</v>
       </c>
       <c r="S94" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="95" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H95" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I95" t="s">
         <v>86</v>
@@ -93342,12 +93345,12 @@
         <v>0.30945</v>
       </c>
       <c r="S95" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="96" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H96" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I96" t="s">
         <v>87</v>
@@ -93365,12 +93368,12 @@
         <v>0.30315000000000003</v>
       </c>
       <c r="S96" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="97" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H97" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I97" t="s">
         <v>88</v>
@@ -93388,12 +93391,12 @@
         <v>0.32484999999999997</v>
       </c>
       <c r="S97" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="98" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H98" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I98" t="s">
         <v>89</v>
@@ -93411,12 +93414,12 @@
         <v>0.18835000000000002</v>
       </c>
       <c r="S98" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="99" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H99" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I99" t="s">
         <v>90</v>
@@ -93434,12 +93437,12 @@
         <v>0.16310000000000002</v>
       </c>
       <c r="S99" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="100" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H100" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I100" t="s">
         <v>91</v>
@@ -93457,12 +93460,12 @@
         <v>0.2392</v>
       </c>
       <c r="S100" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="101" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H101" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I101" t="s">
         <v>92</v>
@@ -93480,12 +93483,12 @@
         <v>0.2792</v>
       </c>
       <c r="S101" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="102" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H102" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I102" t="s">
         <v>93</v>
@@ -93503,12 +93506,12 @@
         <v>0.25224999999999997</v>
       </c>
       <c r="S102" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="103" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H103" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I103" t="s">
         <v>94</v>
@@ -93526,12 +93529,12 @@
         <v>0.28939999999999999</v>
       </c>
       <c r="S103" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="104" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H104" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I104" t="s">
         <v>95</v>
@@ -93549,12 +93552,12 @@
         <v>0.16775000000000001</v>
       </c>
       <c r="S104" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="105" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H105" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I105" t="s">
         <v>96</v>
@@ -93572,12 +93575,12 @@
         <v>0.14505000000000001</v>
       </c>
       <c r="S105" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="106" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H106" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I106" t="s">
         <v>97</v>
@@ -93595,12 +93598,12 @@
         <v>0.24359999999999998</v>
       </c>
       <c r="S106" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="107" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H107" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I107" t="s">
         <v>98</v>
@@ -93618,12 +93621,12 @@
         <v>0.35544999999999999</v>
       </c>
       <c r="S107" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="108" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H108" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I108" t="s">
         <v>99</v>
@@ -93641,12 +93644,12 @@
         <v>0.28994999999999999</v>
       </c>
       <c r="S108" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="109" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H109" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I109" t="s">
         <v>100</v>
@@ -93664,12 +93667,12 @@
         <v>0.31855</v>
       </c>
       <c r="S109" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="110" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H110" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I110" t="s">
         <v>101</v>
@@ -93687,12 +93690,12 @@
         <v>0.183</v>
       </c>
       <c r="S110" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="111" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H111" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I111" t="s">
         <v>102</v>
@@ -93710,12 +93713,12 @@
         <v>0.13450000000000001</v>
       </c>
       <c r="S111" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="112" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H112" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I112" t="s">
         <v>103</v>
@@ -93733,12 +93736,12 @@
         <v>0.25585000000000002</v>
       </c>
       <c r="S112" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="113" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H113" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I113" t="s">
         <v>104</v>
@@ -93756,12 +93759,12 @@
         <v>0.37395</v>
       </c>
       <c r="S113" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="114" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H114" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I114" t="s">
         <v>105</v>
@@ -93779,12 +93782,12 @@
         <v>0.28594999999999998</v>
       </c>
       <c r="S114" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="115" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H115" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I115" t="s">
         <v>106</v>
@@ -93802,12 +93805,12 @@
         <v>0.32190000000000002</v>
       </c>
       <c r="S115" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="116" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H116" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I116" t="s">
         <v>107</v>
@@ -93825,12 +93828,12 @@
         <v>0.21550000000000002</v>
       </c>
       <c r="S116" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="117" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H117" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I117" t="s">
         <v>108</v>
@@ -93848,12 +93851,12 @@
         <v>0.19924999999999998</v>
       </c>
       <c r="S117" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="118" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H118" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I118" t="s">
         <v>109</v>
@@ -93871,12 +93874,12 @@
         <v>0.28159999999999996</v>
       </c>
       <c r="S118" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="119" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H119" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I119" t="s">
         <v>110</v>
@@ -93894,12 +93897,12 @@
         <v>0.41005000000000003</v>
       </c>
       <c r="S119" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="120" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H120" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I120" t="s">
         <v>111</v>
@@ -93917,12 +93920,12 @@
         <v>0.34389999999999998</v>
       </c>
       <c r="S120" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="121" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H121" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I121" t="s">
         <v>112</v>
@@ -93940,12 +93943,12 @@
         <v>0.39655000000000001</v>
       </c>
       <c r="S121" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="122" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H122" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I122" t="s">
         <v>113</v>
@@ -93963,12 +93966,12 @@
         <v>0.24129999999999999</v>
       </c>
       <c r="S122" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="123" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H123" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I123" t="s">
         <v>114</v>
@@ -93986,12 +93989,12 @@
         <v>0.2127</v>
       </c>
       <c r="S123" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="124" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H124" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I124" t="s">
         <v>115</v>
@@ -94009,12 +94012,12 @@
         <v>0.30910000000000004</v>
       </c>
       <c r="S124" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="125" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H125" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I125" t="s">
         <v>116</v>
@@ -94032,12 +94035,12 @@
         <v>0.37570000000000003</v>
       </c>
       <c r="S125" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="126" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H126" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I126" t="s">
         <v>117</v>
@@ -94055,12 +94058,12 @@
         <v>0.36940000000000001</v>
       </c>
       <c r="S126" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="127" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H127" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I127" t="s">
         <v>118</v>
@@ -94078,12 +94081,12 @@
         <v>0.33594999999999997</v>
       </c>
       <c r="S127" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="128" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H128" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I128" t="s">
         <v>119</v>
@@ -94101,12 +94104,12 @@
         <v>0.2392</v>
       </c>
       <c r="S128" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="129" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H129" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I129" t="s">
         <v>120</v>
@@ -94124,12 +94127,12 @@
         <v>0.24365000000000001</v>
       </c>
       <c r="S129" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="130" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H130" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I130" t="s">
         <v>121</v>
@@ -94147,7 +94150,7 @@
         <v>0.37475000000000003</v>
       </c>
       <c r="S130" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="131" spans="8:19" x14ac:dyDescent="0.45">
@@ -94161,7 +94164,7 @@
         <v>0.40375</v>
       </c>
       <c r="S131" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="132" spans="8:19" x14ac:dyDescent="0.45">
@@ -94175,7 +94178,7 @@
         <v>0.38624999999999998</v>
       </c>
       <c r="S132" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="133" spans="8:19" x14ac:dyDescent="0.45">
@@ -94189,7 +94192,7 @@
         <v>0.41835</v>
       </c>
       <c r="S133" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="134" spans="8:19" x14ac:dyDescent="0.45">
@@ -94203,7 +94206,7 @@
         <v>0.27644999999999997</v>
       </c>
       <c r="S134" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="135" spans="8:19" x14ac:dyDescent="0.45">
@@ -94217,7 +94220,7 @@
         <v>0.22705</v>
       </c>
       <c r="S135" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="136" spans="8:19" x14ac:dyDescent="0.45">
@@ -94231,7 +94234,7 @@
         <v>0.34904999999999997</v>
       </c>
       <c r="S136" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="137" spans="8:19" x14ac:dyDescent="0.45">
@@ -94245,7 +94248,7 @@
         <v>0.36795</v>
       </c>
       <c r="S137" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="138" spans="8:19" x14ac:dyDescent="0.45">
@@ -94259,7 +94262,7 @@
         <v>0.34635000000000005</v>
       </c>
       <c r="S138" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="139" spans="8:19" x14ac:dyDescent="0.45">
@@ -94273,7 +94276,7 @@
         <v>0.33884999999999998</v>
       </c>
       <c r="S139" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="140" spans="8:19" x14ac:dyDescent="0.45">
@@ -94287,7 +94290,7 @@
         <v>0.21560000000000001</v>
       </c>
       <c r="S140" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="141" spans="8:19" x14ac:dyDescent="0.45">
@@ -94301,7 +94304,7 @@
         <v>0.27174999999999999</v>
       </c>
       <c r="S141" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="142" spans="8:19" x14ac:dyDescent="0.45">
@@ -94315,7 +94318,7 @@
         <v>0.32514999999999999</v>
       </c>
       <c r="S142" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="143" spans="8:19" x14ac:dyDescent="0.45">
@@ -94329,7 +94332,7 @@
         <v>0.37514999999999998</v>
       </c>
       <c r="S143" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="144" spans="8:19" x14ac:dyDescent="0.45">
@@ -94343,7 +94346,7 @@
         <v>0.35560000000000003</v>
       </c>
       <c r="S144" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="145" spans="16:19" x14ac:dyDescent="0.45">
@@ -94357,7 +94360,7 @@
         <v>0.3261</v>
       </c>
       <c r="S145" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="146" spans="16:19" x14ac:dyDescent="0.45">
@@ -94371,7 +94374,7 @@
         <v>0.23960000000000001</v>
       </c>
       <c r="S146" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="147" spans="16:19" x14ac:dyDescent="0.45">
@@ -94385,7 +94388,7 @@
         <v>0.1827</v>
       </c>
       <c r="S147" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="148" spans="16:19" x14ac:dyDescent="0.45">
@@ -94399,7 +94402,7 @@
         <v>0.30615000000000003</v>
       </c>
       <c r="S148" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="149" spans="16:19" x14ac:dyDescent="0.45">
@@ -94413,7 +94416,7 @@
         <v>0.39615</v>
       </c>
       <c r="S149" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="150" spans="16:19" x14ac:dyDescent="0.45">
@@ -94427,7 +94430,7 @@
         <v>0.34089999999999998</v>
       </c>
       <c r="S150" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="151" spans="16:19" x14ac:dyDescent="0.45">
@@ -94441,7 +94444,7 @@
         <v>0.37814999999999999</v>
       </c>
       <c r="S151" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="152" spans="16:19" x14ac:dyDescent="0.45">
@@ -94455,7 +94458,7 @@
         <v>0.27615000000000001</v>
       </c>
       <c r="S152" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="153" spans="16:19" x14ac:dyDescent="0.45">
@@ -94469,7 +94472,7 @@
         <v>0.16950000000000001</v>
       </c>
       <c r="S153" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="154" spans="16:19" x14ac:dyDescent="0.45">
@@ -94483,7 +94486,7 @@
         <v>0.31430000000000002</v>
       </c>
       <c r="S154" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="155" spans="16:19" x14ac:dyDescent="0.45">
@@ -94497,7 +94500,7 @@
         <v>0.40564999999999996</v>
       </c>
       <c r="S155" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="156" spans="16:19" x14ac:dyDescent="0.45">
@@ -94511,7 +94514,7 @@
         <v>0.39844999999999997</v>
       </c>
       <c r="S156" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="157" spans="16:19" x14ac:dyDescent="0.45">
@@ -94525,7 +94528,7 @@
         <v>0.38795000000000002</v>
       </c>
       <c r="S157" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="158" spans="16:19" x14ac:dyDescent="0.45">
@@ -94539,7 +94542,7 @@
         <v>0.28465000000000001</v>
       </c>
       <c r="S158" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="159" spans="16:19" x14ac:dyDescent="0.45">
@@ -94553,7 +94556,7 @@
         <v>0.2137</v>
       </c>
       <c r="S159" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="160" spans="16:19" x14ac:dyDescent="0.45">
@@ -94567,7 +94570,7 @@
         <v>0.34945000000000004</v>
       </c>
       <c r="S160" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="161" spans="16:19" x14ac:dyDescent="0.45">
@@ -94581,7 +94584,7 @@
         <v>0.33665</v>
       </c>
       <c r="S161" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="162" spans="16:19" x14ac:dyDescent="0.45">
@@ -94595,7 +94598,7 @@
         <v>0.3342</v>
       </c>
       <c r="S162" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="163" spans="16:19" x14ac:dyDescent="0.45">
@@ -94609,7 +94612,7 @@
         <v>0.35009999999999997</v>
       </c>
       <c r="S163" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="164" spans="16:19" x14ac:dyDescent="0.45">
@@ -94623,7 +94626,7 @@
         <v>0.23935000000000001</v>
       </c>
       <c r="S164" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="165" spans="16:19" x14ac:dyDescent="0.45">
@@ -94637,7 +94640,7 @@
         <v>0.17025000000000001</v>
       </c>
       <c r="S165" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="166" spans="16:19" x14ac:dyDescent="0.45">
@@ -94651,7 +94654,7 @@
         <v>0.25659999999999999</v>
       </c>
       <c r="S166" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="167" spans="16:19" x14ac:dyDescent="0.45">
@@ -94665,7 +94668,7 @@
         <v>0.31140000000000001</v>
       </c>
       <c r="S167" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="168" spans="16:19" x14ac:dyDescent="0.45">
@@ -94679,7 +94682,7 @@
         <v>0.28869999999999996</v>
       </c>
       <c r="S168" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="169" spans="16:19" x14ac:dyDescent="0.45">
@@ -94693,7 +94696,7 @@
         <v>0.29415000000000002</v>
       </c>
       <c r="S169" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="170" spans="16:19" x14ac:dyDescent="0.45">
@@ -94707,7 +94710,7 @@
         <v>0.1656</v>
       </c>
       <c r="S170" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="171" spans="16:19" x14ac:dyDescent="0.45">
@@ -94721,7 +94724,7 @@
         <v>0.19540000000000002</v>
       </c>
       <c r="S171" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="172" spans="16:19" x14ac:dyDescent="0.45">
@@ -94735,7 +94738,7 @@
         <v>0.2676</v>
       </c>
       <c r="S172" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="173" spans="16:19" x14ac:dyDescent="0.45">
@@ -94749,7 +94752,7 @@
         <v>0.27474999999999999</v>
       </c>
       <c r="S173" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="174" spans="16:19" x14ac:dyDescent="0.45">
@@ -94763,7 +94766,7 @@
         <v>0.28739999999999999</v>
       </c>
       <c r="S174" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="175" spans="16:19" x14ac:dyDescent="0.45">
@@ -94777,7 +94780,7 @@
         <v>0.32619999999999999</v>
       </c>
       <c r="S175" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="176" spans="16:19" x14ac:dyDescent="0.45">
@@ -94791,7 +94794,7 @@
         <v>0.22685</v>
       </c>
       <c r="S176" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="177" spans="16:19" x14ac:dyDescent="0.45">
@@ -94805,7 +94808,7 @@
         <v>0.1888</v>
       </c>
       <c r="S177" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="178" spans="16:19" x14ac:dyDescent="0.45">
@@ -94819,7 +94822,7 @@
         <v>0.2797</v>
       </c>
       <c r="S178" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="179" spans="16:19" x14ac:dyDescent="0.45">
@@ -94833,7 +94836,7 @@
         <v>0.31764999999999999</v>
       </c>
       <c r="S179" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="180" spans="16:19" x14ac:dyDescent="0.45">
@@ -94847,7 +94850,7 @@
         <v>0.28995000000000004</v>
       </c>
       <c r="S180" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="181" spans="16:19" x14ac:dyDescent="0.45">
@@ -94861,7 +94864,7 @@
         <v>0.31175000000000003</v>
       </c>
       <c r="S181" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="182" spans="16:19" x14ac:dyDescent="0.45">
@@ -94875,7 +94878,7 @@
         <v>0.31035000000000001</v>
       </c>
       <c r="S182" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="183" spans="16:19" x14ac:dyDescent="0.45">
@@ -94889,7 +94892,7 @@
         <v>0.187</v>
       </c>
       <c r="S183" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="184" spans="16:19" x14ac:dyDescent="0.45">
@@ -94903,7 +94906,7 @@
         <v>0.25474999999999998</v>
       </c>
       <c r="S184" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_FRA_grids_kan25/SuppXLS/Scen_TSParameters_ts_60.xlsx
+++ b/VerveStacks_FRA_grids_kan25/SuppXLS/Scen_TSParameters_ts_60.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_FRA_grids_kan25\SuppXLS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_FRA_grids_kan25\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8DC4D69-B78E-4D11-97C2-F276656B5AB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{22B287D4-506B-43CE-B818-E6929B5077E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -894,13 +894,19 @@
     <t>D</t>
   </si>
   <si>
-    <t>S01aH04,S01aH07,S02aH07,S02aH04,S02aH05,S06aH07,S04aH06,S05aH04,S06aH02,S06aH03,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S03aH02,S03aH04,S04aH02,S03aH03,S04aH05,S04aH08,S04aH03,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S01aH06,S02aH03,S05aH07,S02aH02,S06aH06,S01aH02,S04aH04,S01aH03,S05aH02,S05aH03,S05aH06,S05aH08</t>
+    <t>S02aH04,S02aH05,S06aH07,S01aH03,S05aH02,S05aH03,S05aH06,S03aH02,S05aH08,S01aH04,S01aH07,S02aH07,S02aH02,S06aH06,S04aH03,S03aH03,S04aH06,S05aH04,S06aH02,S06aH03,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S03aH04,S04aH02,S01aH02,S04aH04,S01aH06,S02aH03,S05aH07,S04aH05,S04aH08</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S01aH09,S03aH08,S03aH10,S06aH08,S06aH09,S01aH02,S05aH10,S04aH02,S02aH09,S04aH09,S05aH01,S01aH10,S03aH02,S02aH02,S04aH10,S06aH10,S05aH08,S02aH01,S02aH10,S05aH02,S03aH09,S05aH09,S01aH01,S04aH01,S06aH02,S03aH01,S01aH08,S02aH08,S04aH08,S06aH01</t>
+    <t>S03aH08,S03aH10,S06aH08,S04aH02,S04aH08,S06aH01,S01aH09,S03aH01,S02aH01,S02aH10,S05aH02,S02aH02,S04aH10,S06aH10,S06aH09,S01aH02,S05aH10,S03aH09,S05aH09,S02aH09,S04aH09,S05aH01,S01aH10,S03aH02,S01aH08,S02aH08,S01aH01,S04aH01,S06aH02,S05aH08</t>
+  </si>
+  <si>
+    <t>elc_buildings</t>
+  </si>
+  <si>
+    <t>elc_industry</t>
   </si>
   <si>
     <t>com_pkflx</t>
@@ -916,12 +922,6 @@
   </si>
   <si>
     <t>hydro</t>
-  </si>
-  <si>
-    <t>*[_]buildings</t>
-  </si>
-  <si>
-    <t>*[_]industry</t>
   </si>
 </sst>
 </file>
@@ -1495,7 +1495,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S01aH09,S03aH08,S03aH10,S06aH08,S06aH09,S01aH02,S05aH10,S04aH02,S02aH09,S04aH09,S05aH01,S01aH10,S03aH02,S02aH02,S04aH10,S06aH10,S05aH08,S02aH01,S02aH10,S05aH02,S03aH09,S05aH09,S01aH01,S04aH01,S06aH02,S03aH01,S01aH08,S02aH08,S04aH08,S06aH01</v>
+        <v>S03aH08,S03aH10,S06aH08,S04aH02,S04aH08,S06aH01,S01aH09,S03aH01,S02aH01,S02aH10,S05aH02,S02aH02,S04aH10,S06aH10,S06aH09,S01aH02,S05aH10,S03aH09,S05aH09,S02aH09,S04aH09,S05aH01,S01aH10,S03aH02,S01aH08,S02aH08,S01aH01,S04aH01,S06aH02,S05aH08</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S01aH04,S01aH07,S02aH07,S02aH04,S02aH05,S06aH07,S04aH06,S05aH04,S06aH02,S06aH03,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S03aH02,S03aH04,S04aH02,S03aH03,S04aH05,S04aH08,S04aH03,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S01aH06,S02aH03,S05aH07,S02aH02,S06aH06,S01aH02,S04aH04,S01aH03,S05aH02,S05aH03,S05aH06,S05aH08</v>
+        <v>S02aH04,S02aH05,S06aH07,S01aH03,S05aH02,S05aH03,S05aH06,S03aH02,S05aH08,S01aH04,S01aH07,S02aH07,S02aH02,S06aH06,S04aH03,S03aH03,S04aH06,S05aH04,S06aH02,S06aH03,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S03aH04,S04aH02,S01aH02,S04aH04,S01aH06,S02aH03,S05aH07,S04aH05,S04aH08</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1623,7 +1623,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6306E1CB-7CFF-4AA4-A07F-B5974934C366}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1968FEB7-0762-4BD1-86AD-190E232BE042}">
   <dimension ref="A9:G20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1767,7 +1767,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07203A8B-8E9F-4DC1-AEAE-2FF5A6BCA5B7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A41CD9F-4922-4E38-BA49-A19200029C46}">
   <dimension ref="B9:O1810"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -59429,7 +59429,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57F36EE6-0455-4B5C-A5AE-09DB82B698E3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F547557-E2C1-48A7-AC96-959801F5F7FF}">
   <dimension ref="B9:IV85"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -90057,12 +90057,9 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7CCA5E0-2F8D-4862-8873-589F84DB6C7F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32A7EEA1-4124-4127-8C0A-80A5F134130D}">
   <dimension ref="A9:S184"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="8" max="8" width="12.1328125" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="9" spans="1:19" x14ac:dyDescent="0.45">
       <c r="C9" t="str">
@@ -90070,8 +90067,8 @@
         <v>~TFM_DINS-AT</v>
       </c>
       <c r="H9" t="str">
-        <f>IF(A11="x","DeActivated","~TFM_INS-AT:cset_set=DEM")</f>
-        <v>~TFM_INS-AT:cset_set=DEM</v>
+        <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
+        <v>~TFM_DINS-AT</v>
       </c>
       <c r="L9" t="str">
         <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
@@ -90114,19 +90111,19 @@
         <v>57</v>
       </c>
       <c r="N10" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="P10" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q10" t="s">
         <v>57</v>
       </c>
       <c r="R10" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="S10" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.45">
@@ -90147,7 +90144,7 @@
         <v>281</v>
       </c>
       <c r="H11" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I11" t="s">
         <v>61</v>
@@ -90174,7 +90171,7 @@
         <v>0.32884999999999998</v>
       </c>
       <c r="S11" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.45">
@@ -90191,7 +90188,7 @@
         <v>281</v>
       </c>
       <c r="H12" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I12" t="s">
         <v>63</v>
@@ -90218,7 +90215,7 @@
         <v>0.32379999999999998</v>
       </c>
       <c r="S12" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.45">
@@ -90235,7 +90232,7 @@
         <v>281</v>
       </c>
       <c r="H13" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I13" t="s">
         <v>64</v>
@@ -90262,7 +90259,7 @@
         <v>0.33195000000000002</v>
       </c>
       <c r="S13" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.45">
@@ -90279,7 +90276,7 @@
         <v>281</v>
       </c>
       <c r="H14" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I14" t="s">
         <v>65</v>
@@ -90306,7 +90303,7 @@
         <v>0.20910000000000001</v>
       </c>
       <c r="S14" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.45">
@@ -90323,7 +90320,7 @@
         <v>281</v>
       </c>
       <c r="H15" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I15" t="s">
         <v>66</v>
@@ -90350,7 +90347,7 @@
         <v>0.20760000000000001</v>
       </c>
       <c r="S15" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.45">
@@ -90367,7 +90364,7 @@
         <v>281</v>
       </c>
       <c r="H16" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I16" t="s">
         <v>67</v>
@@ -90394,7 +90391,7 @@
         <v>0.26144999999999996</v>
       </c>
       <c r="S16" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="17" spans="3:19" x14ac:dyDescent="0.45">
@@ -90411,7 +90408,7 @@
         <v>281</v>
       </c>
       <c r="H17" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I17" t="s">
         <v>68</v>
@@ -90438,7 +90435,7 @@
         <v>0.38249999999999995</v>
       </c>
       <c r="S17" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="18" spans="3:19" x14ac:dyDescent="0.45">
@@ -90455,7 +90452,7 @@
         <v>281</v>
       </c>
       <c r="H18" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I18" t="s">
         <v>69</v>
@@ -90482,7 +90479,7 @@
         <v>0.25664999999999999</v>
       </c>
       <c r="S18" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="19" spans="3:19" x14ac:dyDescent="0.45">
@@ -90499,7 +90496,7 @@
         <v>281</v>
       </c>
       <c r="H19" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I19" t="s">
         <v>70</v>
@@ -90526,7 +90523,7 @@
         <v>0.32330000000000003</v>
       </c>
       <c r="S19" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="20" spans="3:19" x14ac:dyDescent="0.45">
@@ -90543,7 +90540,7 @@
         <v>281</v>
       </c>
       <c r="H20" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I20" t="s">
         <v>71</v>
@@ -90570,7 +90567,7 @@
         <v>0.251</v>
       </c>
       <c r="S20" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="21" spans="3:19" x14ac:dyDescent="0.45">
@@ -90587,7 +90584,7 @@
         <v>281</v>
       </c>
       <c r="H21" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I21" t="s">
         <v>72</v>
@@ -90614,7 +90611,7 @@
         <v>0.16105</v>
       </c>
       <c r="S21" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="22" spans="3:19" x14ac:dyDescent="0.45">
@@ -90631,7 +90628,7 @@
         <v>281</v>
       </c>
       <c r="H22" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I22" t="s">
         <v>73</v>
@@ -90658,7 +90655,7 @@
         <v>0.21995000000000001</v>
       </c>
       <c r="S22" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="23" spans="3:19" x14ac:dyDescent="0.45">
@@ -90675,7 +90672,7 @@
         <v>281</v>
       </c>
       <c r="H23" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I23" t="s">
         <v>74</v>
@@ -90702,7 +90699,7 @@
         <v>0.25940000000000002</v>
       </c>
       <c r="S23" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="24" spans="3:19" x14ac:dyDescent="0.45">
@@ -90719,7 +90716,7 @@
         <v>281</v>
       </c>
       <c r="H24" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I24" t="s">
         <v>75</v>
@@ -90746,7 +90743,7 @@
         <v>0.23335</v>
       </c>
       <c r="S24" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="25" spans="3:19" x14ac:dyDescent="0.45">
@@ -90763,7 +90760,7 @@
         <v>281</v>
       </c>
       <c r="H25" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I25" t="s">
         <v>76</v>
@@ -90790,7 +90787,7 @@
         <v>0.22620000000000001</v>
       </c>
       <c r="S25" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="26" spans="3:19" x14ac:dyDescent="0.45">
@@ -90807,7 +90804,7 @@
         <v>281</v>
       </c>
       <c r="H26" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I26" t="s">
         <v>77</v>
@@ -90834,7 +90831,7 @@
         <v>0.15055000000000002</v>
       </c>
       <c r="S26" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="27" spans="3:19" x14ac:dyDescent="0.45">
@@ -90851,7 +90848,7 @@
         <v>281</v>
       </c>
       <c r="H27" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I27" t="s">
         <v>78</v>
@@ -90878,7 +90875,7 @@
         <v>0.13195000000000001</v>
       </c>
       <c r="S27" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" spans="3:19" x14ac:dyDescent="0.45">
@@ -90895,7 +90892,7 @@
         <v>281</v>
       </c>
       <c r="H28" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I28" t="s">
         <v>79</v>
@@ -90922,7 +90919,7 @@
         <v>0.21455000000000002</v>
       </c>
       <c r="S28" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="3:19" x14ac:dyDescent="0.45">
@@ -90939,7 +90936,7 @@
         <v>281</v>
       </c>
       <c r="H29" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I29" t="s">
         <v>80</v>
@@ -90966,7 +90963,7 @@
         <v>0.34404999999999997</v>
       </c>
       <c r="S29" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="30" spans="3:19" x14ac:dyDescent="0.45">
@@ -90983,7 +90980,7 @@
         <v>281</v>
       </c>
       <c r="H30" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I30" t="s">
         <v>81</v>
@@ -91010,7 +91007,7 @@
         <v>0.26339999999999997</v>
       </c>
       <c r="S30" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="3:19" x14ac:dyDescent="0.45">
@@ -91027,7 +91024,7 @@
         <v>281</v>
       </c>
       <c r="H31" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I31" t="s">
         <v>82</v>
@@ -91054,7 +91051,7 @@
         <v>0.3</v>
       </c>
       <c r="S31" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="32" spans="3:19" x14ac:dyDescent="0.45">
@@ -91071,7 +91068,7 @@
         <v>281</v>
       </c>
       <c r="H32" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I32" t="s">
         <v>83</v>
@@ -91098,7 +91095,7 @@
         <v>0.192</v>
       </c>
       <c r="S32" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="33" spans="3:19" x14ac:dyDescent="0.45">
@@ -91115,7 +91112,7 @@
         <v>281</v>
       </c>
       <c r="H33" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I33" t="s">
         <v>84</v>
@@ -91142,7 +91139,7 @@
         <v>0.18359999999999999</v>
       </c>
       <c r="S33" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="34" spans="3:19" x14ac:dyDescent="0.45">
@@ -91159,7 +91156,7 @@
         <v>281</v>
       </c>
       <c r="H34" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I34" t="s">
         <v>85</v>
@@ -91186,7 +91183,7 @@
         <v>0.22505</v>
       </c>
       <c r="S34" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="35" spans="3:19" x14ac:dyDescent="0.45">
@@ -91203,7 +91200,7 @@
         <v>281</v>
       </c>
       <c r="H35" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I35" t="s">
         <v>86</v>
@@ -91230,7 +91227,7 @@
         <v>0.3337</v>
       </c>
       <c r="S35" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="36" spans="3:19" x14ac:dyDescent="0.45">
@@ -91247,7 +91244,7 @@
         <v>281</v>
       </c>
       <c r="H36" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I36" t="s">
         <v>87</v>
@@ -91274,7 +91271,7 @@
         <v>0.25495000000000001</v>
       </c>
       <c r="S36" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="37" spans="3:19" x14ac:dyDescent="0.45">
@@ -91291,7 +91288,7 @@
         <v>281</v>
       </c>
       <c r="H37" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I37" t="s">
         <v>88</v>
@@ -91318,7 +91315,7 @@
         <v>0.26024999999999998</v>
       </c>
       <c r="S37" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="38" spans="3:19" x14ac:dyDescent="0.45">
@@ -91335,7 +91332,7 @@
         <v>281</v>
       </c>
       <c r="H38" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I38" t="s">
         <v>89</v>
@@ -91362,7 +91359,7 @@
         <v>0.2064</v>
       </c>
       <c r="S38" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="39" spans="3:19" x14ac:dyDescent="0.45">
@@ -91379,7 +91376,7 @@
         <v>281</v>
       </c>
       <c r="H39" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I39" t="s">
         <v>90</v>
@@ -91406,7 +91403,7 @@
         <v>0.18104999999999999</v>
       </c>
       <c r="S39" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="40" spans="3:19" x14ac:dyDescent="0.45">
@@ -91423,7 +91420,7 @@
         <v>281</v>
       </c>
       <c r="H40" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I40" t="s">
         <v>91</v>
@@ -91450,7 +91447,7 @@
         <v>0.23249999999999998</v>
       </c>
       <c r="S40" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="41" spans="3:19" x14ac:dyDescent="0.45">
@@ -91467,7 +91464,7 @@
         <v>281</v>
       </c>
       <c r="H41" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I41" t="s">
         <v>92</v>
@@ -91494,7 +91491,7 @@
         <v>0.32094999999999996</v>
       </c>
       <c r="S41" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="42" spans="3:19" x14ac:dyDescent="0.45">
@@ -91511,7 +91508,7 @@
         <v>281</v>
       </c>
       <c r="H42" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I42" t="s">
         <v>93</v>
@@ -91538,7 +91535,7 @@
         <v>0.33640000000000003</v>
       </c>
       <c r="S42" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="43" spans="3:19" x14ac:dyDescent="0.45">
@@ -91555,7 +91552,7 @@
         <v>281</v>
       </c>
       <c r="H43" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I43" t="s">
         <v>94</v>
@@ -91582,7 +91579,7 @@
         <v>0.3276</v>
       </c>
       <c r="S43" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="44" spans="3:19" x14ac:dyDescent="0.45">
@@ -91599,7 +91596,7 @@
         <v>281</v>
       </c>
       <c r="H44" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I44" t="s">
         <v>95</v>
@@ -91626,7 +91623,7 @@
         <v>0.18459999999999999</v>
       </c>
       <c r="S44" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="45" spans="3:19" x14ac:dyDescent="0.45">
@@ -91643,7 +91640,7 @@
         <v>281</v>
       </c>
       <c r="H45" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I45" t="s">
         <v>96</v>
@@ -91670,7 +91667,7 @@
         <v>0.20365</v>
       </c>
       <c r="S45" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="46" spans="3:19" x14ac:dyDescent="0.45">
@@ -91687,7 +91684,7 @@
         <v>281</v>
       </c>
       <c r="H46" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I46" t="s">
         <v>97</v>
@@ -91714,7 +91711,7 @@
         <v>0.23815000000000003</v>
       </c>
       <c r="S46" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="47" spans="3:19" x14ac:dyDescent="0.45">
@@ -91731,7 +91728,7 @@
         <v>281</v>
       </c>
       <c r="H47" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I47" t="s">
         <v>98</v>
@@ -91758,7 +91755,7 @@
         <v>0.3876</v>
       </c>
       <c r="S47" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="48" spans="3:19" x14ac:dyDescent="0.45">
@@ -91775,7 +91772,7 @@
         <v>281</v>
       </c>
       <c r="H48" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I48" t="s">
         <v>99</v>
@@ -91802,7 +91799,7 @@
         <v>0.33899999999999997</v>
       </c>
       <c r="S48" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="49" spans="3:19" x14ac:dyDescent="0.45">
@@ -91819,7 +91816,7 @@
         <v>281</v>
       </c>
       <c r="H49" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I49" t="s">
         <v>100</v>
@@ -91846,7 +91843,7 @@
         <v>0.35389999999999999</v>
       </c>
       <c r="S49" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="50" spans="3:19" x14ac:dyDescent="0.45">
@@ -91863,7 +91860,7 @@
         <v>281</v>
       </c>
       <c r="H50" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I50" t="s">
         <v>101</v>
@@ -91890,7 +91887,7 @@
         <v>0.21375</v>
       </c>
       <c r="S50" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="51" spans="3:19" x14ac:dyDescent="0.45">
@@ -91907,7 +91904,7 @@
         <v>281</v>
       </c>
       <c r="H51" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I51" t="s">
         <v>102</v>
@@ -91934,7 +91931,7 @@
         <v>0.18010000000000001</v>
       </c>
       <c r="S51" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="52" spans="3:19" x14ac:dyDescent="0.45">
@@ -91951,7 +91948,7 @@
         <v>281</v>
       </c>
       <c r="H52" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I52" t="s">
         <v>103</v>
@@ -91978,7 +91975,7 @@
         <v>0.26650000000000001</v>
       </c>
       <c r="S52" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="53" spans="3:19" x14ac:dyDescent="0.45">
@@ -91995,7 +91992,7 @@
         <v>281</v>
       </c>
       <c r="H53" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I53" t="s">
         <v>104</v>
@@ -92022,7 +92019,7 @@
         <v>0.34970000000000001</v>
       </c>
       <c r="S53" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="54" spans="3:19" x14ac:dyDescent="0.45">
@@ -92039,7 +92036,7 @@
         <v>281</v>
       </c>
       <c r="H54" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I54" t="s">
         <v>105</v>
@@ -92066,7 +92063,7 @@
         <v>0.32765</v>
       </c>
       <c r="S54" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="55" spans="3:19" x14ac:dyDescent="0.45">
@@ -92083,7 +92080,7 @@
         <v>281</v>
       </c>
       <c r="H55" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I55" t="s">
         <v>106</v>
@@ -92110,7 +92107,7 @@
         <v>0.36409999999999998</v>
       </c>
       <c r="S55" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="56" spans="3:19" x14ac:dyDescent="0.45">
@@ -92127,7 +92124,7 @@
         <v>281</v>
       </c>
       <c r="H56" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I56" t="s">
         <v>107</v>
@@ -92154,7 +92151,7 @@
         <v>0.19919999999999999</v>
       </c>
       <c r="S56" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="57" spans="3:19" x14ac:dyDescent="0.45">
@@ -92171,7 +92168,7 @@
         <v>281</v>
       </c>
       <c r="H57" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I57" t="s">
         <v>108</v>
@@ -92198,7 +92195,7 @@
         <v>0.1653</v>
       </c>
       <c r="S57" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="58" spans="3:19" x14ac:dyDescent="0.45">
@@ -92215,7 +92212,7 @@
         <v>281</v>
       </c>
       <c r="H58" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I58" t="s">
         <v>109</v>
@@ -92242,7 +92239,7 @@
         <v>0.21804999999999999</v>
       </c>
       <c r="S58" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="59" spans="3:19" x14ac:dyDescent="0.45">
@@ -92259,7 +92256,7 @@
         <v>281</v>
       </c>
       <c r="H59" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I59" t="s">
         <v>110</v>
@@ -92286,7 +92283,7 @@
         <v>0.30020000000000002</v>
       </c>
       <c r="S59" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="60" spans="3:19" x14ac:dyDescent="0.45">
@@ -92303,7 +92300,7 @@
         <v>281</v>
       </c>
       <c r="H60" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I60" t="s">
         <v>111</v>
@@ -92330,7 +92327,7 @@
         <v>0.34819999999999995</v>
       </c>
       <c r="S60" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="61" spans="3:19" x14ac:dyDescent="0.45">
@@ -92347,7 +92344,7 @@
         <v>281</v>
       </c>
       <c r="H61" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I61" t="s">
         <v>112</v>
@@ -92374,7 +92371,7 @@
         <v>0.36664999999999998</v>
       </c>
       <c r="S61" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="62" spans="3:19" x14ac:dyDescent="0.45">
@@ -92391,7 +92388,7 @@
         <v>281</v>
       </c>
       <c r="H62" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I62" t="s">
         <v>113</v>
@@ -92418,7 +92415,7 @@
         <v>0.2026</v>
       </c>
       <c r="S62" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="63" spans="3:19" x14ac:dyDescent="0.45">
@@ -92435,7 +92432,7 @@
         <v>281</v>
       </c>
       <c r="H63" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I63" t="s">
         <v>114</v>
@@ -92462,7 +92459,7 @@
         <v>0.18235000000000001</v>
       </c>
       <c r="S63" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="64" spans="3:19" x14ac:dyDescent="0.45">
@@ -92479,7 +92476,7 @@
         <v>281</v>
       </c>
       <c r="H64" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I64" t="s">
         <v>115</v>
@@ -92506,7 +92503,7 @@
         <v>0.29704999999999998</v>
       </c>
       <c r="S64" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="65" spans="3:19" x14ac:dyDescent="0.45">
@@ -92523,7 +92520,7 @@
         <v>281</v>
       </c>
       <c r="H65" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I65" t="s">
         <v>116</v>
@@ -92550,7 +92547,7 @@
         <v>0.33479999999999999</v>
       </c>
       <c r="S65" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="66" spans="3:19" x14ac:dyDescent="0.45">
@@ -92567,7 +92564,7 @@
         <v>281</v>
       </c>
       <c r="H66" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I66" t="s">
         <v>117</v>
@@ -92594,7 +92591,7 @@
         <v>0.33210000000000001</v>
       </c>
       <c r="S66" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="67" spans="3:19" x14ac:dyDescent="0.45">
@@ -92611,7 +92608,7 @@
         <v>281</v>
       </c>
       <c r="H67" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I67" t="s">
         <v>118</v>
@@ -92638,7 +92635,7 @@
         <v>0.34714999999999996</v>
       </c>
       <c r="S67" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="68" spans="3:19" x14ac:dyDescent="0.45">
@@ -92655,7 +92652,7 @@
         <v>281</v>
       </c>
       <c r="H68" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I68" t="s">
         <v>119</v>
@@ -92682,7 +92679,7 @@
         <v>0.24829999999999999</v>
       </c>
       <c r="S68" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="69" spans="3:19" x14ac:dyDescent="0.45">
@@ -92699,7 +92696,7 @@
         <v>281</v>
       </c>
       <c r="H69" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I69" t="s">
         <v>120</v>
@@ -92726,7 +92723,7 @@
         <v>0.17255000000000001</v>
       </c>
       <c r="S69" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="70" spans="3:19" x14ac:dyDescent="0.45">
@@ -92743,7 +92740,7 @@
         <v>281</v>
       </c>
       <c r="H70" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I70" t="s">
         <v>121</v>
@@ -92770,12 +92767,12 @@
         <v>0.29925000000000002</v>
       </c>
       <c r="S70" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="71" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H71" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I71" t="s">
         <v>61</v>
@@ -92793,12 +92790,12 @@
         <v>0.30010000000000003</v>
       </c>
       <c r="S71" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="72" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H72" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I72" t="s">
         <v>63</v>
@@ -92816,12 +92813,12 @@
         <v>0.23294999999999999</v>
       </c>
       <c r="S72" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="73" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H73" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I73" t="s">
         <v>64</v>
@@ -92839,12 +92836,12 @@
         <v>0.28615000000000002</v>
       </c>
       <c r="S73" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="74" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H74" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I74" t="s">
         <v>65</v>
@@ -92862,12 +92859,12 @@
         <v>0.20265</v>
       </c>
       <c r="S74" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="75" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H75" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I75" t="s">
         <v>66</v>
@@ -92885,12 +92882,12 @@
         <v>0.152</v>
       </c>
       <c r="S75" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="76" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H76" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I76" t="s">
         <v>67</v>
@@ -92908,12 +92905,12 @@
         <v>0.24084999999999998</v>
       </c>
       <c r="S76" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="77" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H77" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I77" t="s">
         <v>68</v>
@@ -92931,12 +92928,12 @@
         <v>0.30495</v>
       </c>
       <c r="S77" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="78" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H78" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I78" t="s">
         <v>69</v>
@@ -92954,12 +92951,12 @@
         <v>0.33194999999999997</v>
       </c>
       <c r="S78" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="79" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H79" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I79" t="s">
         <v>70</v>
@@ -92977,12 +92974,12 @@
         <v>0.31174999999999997</v>
       </c>
       <c r="S79" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="80" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H80" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I80" t="s">
         <v>71</v>
@@ -93000,12 +92997,12 @@
         <v>0.24269999999999997</v>
       </c>
       <c r="S80" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="81" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H81" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I81" t="s">
         <v>72</v>
@@ -93023,12 +93020,12 @@
         <v>0.1401</v>
       </c>
       <c r="S81" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="82" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H82" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I82" t="s">
         <v>73</v>
@@ -93046,12 +93043,12 @@
         <v>0.26954999999999996</v>
       </c>
       <c r="S82" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="83" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H83" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I83" t="s">
         <v>74</v>
@@ -93069,12 +93066,12 @@
         <v>0.2893</v>
       </c>
       <c r="S83" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="84" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H84" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I84" t="s">
         <v>75</v>
@@ -93092,12 +93089,12 @@
         <v>0.25214999999999999</v>
       </c>
       <c r="S84" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="85" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H85" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I85" t="s">
         <v>76</v>
@@ -93115,12 +93112,12 @@
         <v>0.28079999999999999</v>
       </c>
       <c r="S85" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="86" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H86" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I86" t="s">
         <v>77</v>
@@ -93138,12 +93135,12 @@
         <v>0.2311</v>
       </c>
       <c r="S86" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="87" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H87" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I87" t="s">
         <v>78</v>
@@ -93161,12 +93158,12 @@
         <v>0.10925</v>
       </c>
       <c r="S87" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="88" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H88" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I88" t="s">
         <v>79</v>
@@ -93184,12 +93181,12 @@
         <v>0.24104999999999999</v>
       </c>
       <c r="S88" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="89" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H89" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I89" t="s">
         <v>80</v>
@@ -93207,12 +93204,12 @@
         <v>0.30325000000000002</v>
       </c>
       <c r="S89" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="90" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H90" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I90" t="s">
         <v>81</v>
@@ -93230,12 +93227,12 @@
         <v>0.34694999999999998</v>
       </c>
       <c r="S90" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="91" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H91" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I91" t="s">
         <v>82</v>
@@ -93253,12 +93250,12 @@
         <v>0.30105000000000004</v>
       </c>
       <c r="S91" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="92" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H92" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I92" t="s">
         <v>83</v>
@@ -93276,12 +93273,12 @@
         <v>0.23320000000000002</v>
       </c>
       <c r="S92" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="93" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H93" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I93" t="s">
         <v>84</v>
@@ -93299,12 +93296,12 @@
         <v>0.16464999999999999</v>
       </c>
       <c r="S93" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="94" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H94" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I94" t="s">
         <v>85</v>
@@ -93322,12 +93319,12 @@
         <v>0.2283</v>
       </c>
       <c r="S94" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="95" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H95" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I95" t="s">
         <v>86</v>
@@ -93345,12 +93342,12 @@
         <v>0.30945</v>
       </c>
       <c r="S95" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="96" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H96" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I96" t="s">
         <v>87</v>
@@ -93368,12 +93365,12 @@
         <v>0.30315000000000003</v>
       </c>
       <c r="S96" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="97" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H97" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I97" t="s">
         <v>88</v>
@@ -93391,12 +93388,12 @@
         <v>0.32484999999999997</v>
       </c>
       <c r="S97" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="98" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H98" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I98" t="s">
         <v>89</v>
@@ -93414,12 +93411,12 @@
         <v>0.18835000000000002</v>
       </c>
       <c r="S98" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="99" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H99" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I99" t="s">
         <v>90</v>
@@ -93437,12 +93434,12 @@
         <v>0.16310000000000002</v>
       </c>
       <c r="S99" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="100" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H100" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I100" t="s">
         <v>91</v>
@@ -93460,12 +93457,12 @@
         <v>0.2392</v>
       </c>
       <c r="S100" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="101" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H101" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I101" t="s">
         <v>92</v>
@@ -93483,12 +93480,12 @@
         <v>0.2792</v>
       </c>
       <c r="S101" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="102" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H102" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I102" t="s">
         <v>93</v>
@@ -93506,12 +93503,12 @@
         <v>0.25224999999999997</v>
       </c>
       <c r="S102" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="103" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H103" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I103" t="s">
         <v>94</v>
@@ -93529,12 +93526,12 @@
         <v>0.28939999999999999</v>
       </c>
       <c r="S103" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="104" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H104" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I104" t="s">
         <v>95</v>
@@ -93552,12 +93549,12 @@
         <v>0.16775000000000001</v>
       </c>
       <c r="S104" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="105" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H105" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I105" t="s">
         <v>96</v>
@@ -93575,12 +93572,12 @@
         <v>0.14505000000000001</v>
       </c>
       <c r="S105" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="106" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H106" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I106" t="s">
         <v>97</v>
@@ -93598,12 +93595,12 @@
         <v>0.24359999999999998</v>
       </c>
       <c r="S106" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="107" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H107" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I107" t="s">
         <v>98</v>
@@ -93621,12 +93618,12 @@
         <v>0.35544999999999999</v>
       </c>
       <c r="S107" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="108" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H108" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I108" t="s">
         <v>99</v>
@@ -93644,12 +93641,12 @@
         <v>0.28994999999999999</v>
       </c>
       <c r="S108" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="109" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H109" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I109" t="s">
         <v>100</v>
@@ -93667,12 +93664,12 @@
         <v>0.31855</v>
       </c>
       <c r="S109" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="110" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H110" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I110" t="s">
         <v>101</v>
@@ -93690,12 +93687,12 @@
         <v>0.183</v>
       </c>
       <c r="S110" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="111" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H111" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I111" t="s">
         <v>102</v>
@@ -93713,12 +93710,12 @@
         <v>0.13450000000000001</v>
       </c>
       <c r="S111" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="112" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H112" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I112" t="s">
         <v>103</v>
@@ -93736,12 +93733,12 @@
         <v>0.25585000000000002</v>
       </c>
       <c r="S112" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="113" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H113" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I113" t="s">
         <v>104</v>
@@ -93759,12 +93756,12 @@
         <v>0.37395</v>
       </c>
       <c r="S113" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="114" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H114" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I114" t="s">
         <v>105</v>
@@ -93782,12 +93779,12 @@
         <v>0.28594999999999998</v>
       </c>
       <c r="S114" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="115" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H115" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I115" t="s">
         <v>106</v>
@@ -93805,12 +93802,12 @@
         <v>0.32190000000000002</v>
       </c>
       <c r="S115" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="116" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H116" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I116" t="s">
         <v>107</v>
@@ -93828,12 +93825,12 @@
         <v>0.21550000000000002</v>
       </c>
       <c r="S116" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="117" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H117" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I117" t="s">
         <v>108</v>
@@ -93851,12 +93848,12 @@
         <v>0.19924999999999998</v>
       </c>
       <c r="S117" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="118" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H118" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I118" t="s">
         <v>109</v>
@@ -93874,12 +93871,12 @@
         <v>0.28159999999999996</v>
       </c>
       <c r="S118" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="119" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H119" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I119" t="s">
         <v>110</v>
@@ -93897,12 +93894,12 @@
         <v>0.41005000000000003</v>
       </c>
       <c r="S119" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="120" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H120" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I120" t="s">
         <v>111</v>
@@ -93920,12 +93917,12 @@
         <v>0.34389999999999998</v>
       </c>
       <c r="S120" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="121" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H121" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I121" t="s">
         <v>112</v>
@@ -93943,12 +93940,12 @@
         <v>0.39655000000000001</v>
       </c>
       <c r="S121" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="122" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H122" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I122" t="s">
         <v>113</v>
@@ -93966,12 +93963,12 @@
         <v>0.24129999999999999</v>
       </c>
       <c r="S122" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="123" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H123" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I123" t="s">
         <v>114</v>
@@ -93989,12 +93986,12 @@
         <v>0.2127</v>
       </c>
       <c r="S123" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="124" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H124" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I124" t="s">
         <v>115</v>
@@ -94012,12 +94009,12 @@
         <v>0.30910000000000004</v>
       </c>
       <c r="S124" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="125" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H125" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I125" t="s">
         <v>116</v>
@@ -94035,12 +94032,12 @@
         <v>0.37570000000000003</v>
       </c>
       <c r="S125" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="126" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H126" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I126" t="s">
         <v>117</v>
@@ -94058,12 +94055,12 @@
         <v>0.36940000000000001</v>
       </c>
       <c r="S126" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="127" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H127" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I127" t="s">
         <v>118</v>
@@ -94081,12 +94078,12 @@
         <v>0.33594999999999997</v>
       </c>
       <c r="S127" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="128" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H128" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I128" t="s">
         <v>119</v>
@@ -94104,12 +94101,12 @@
         <v>0.2392</v>
       </c>
       <c r="S128" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="129" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H129" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I129" t="s">
         <v>120</v>
@@ -94127,12 +94124,12 @@
         <v>0.24365000000000001</v>
       </c>
       <c r="S129" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="130" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H130" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I130" t="s">
         <v>121</v>
@@ -94150,7 +94147,7 @@
         <v>0.37475000000000003</v>
       </c>
       <c r="S130" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="131" spans="8:19" x14ac:dyDescent="0.45">
@@ -94164,7 +94161,7 @@
         <v>0.40375</v>
       </c>
       <c r="S131" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="132" spans="8:19" x14ac:dyDescent="0.45">
@@ -94178,7 +94175,7 @@
         <v>0.38624999999999998</v>
       </c>
       <c r="S132" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="133" spans="8:19" x14ac:dyDescent="0.45">
@@ -94192,7 +94189,7 @@
         <v>0.41835</v>
       </c>
       <c r="S133" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="134" spans="8:19" x14ac:dyDescent="0.45">
@@ -94206,7 +94203,7 @@
         <v>0.27644999999999997</v>
       </c>
       <c r="S134" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="135" spans="8:19" x14ac:dyDescent="0.45">
@@ -94220,7 +94217,7 @@
         <v>0.22705</v>
       </c>
       <c r="S135" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="136" spans="8:19" x14ac:dyDescent="0.45">
@@ -94234,7 +94231,7 @@
         <v>0.34904999999999997</v>
       </c>
       <c r="S136" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="137" spans="8:19" x14ac:dyDescent="0.45">
@@ -94248,7 +94245,7 @@
         <v>0.36795</v>
       </c>
       <c r="S137" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="138" spans="8:19" x14ac:dyDescent="0.45">
@@ -94262,7 +94259,7 @@
         <v>0.34635000000000005</v>
       </c>
       <c r="S138" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="139" spans="8:19" x14ac:dyDescent="0.45">
@@ -94276,7 +94273,7 @@
         <v>0.33884999999999998</v>
       </c>
       <c r="S139" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="140" spans="8:19" x14ac:dyDescent="0.45">
@@ -94290,7 +94287,7 @@
         <v>0.21560000000000001</v>
       </c>
       <c r="S140" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="141" spans="8:19" x14ac:dyDescent="0.45">
@@ -94304,7 +94301,7 @@
         <v>0.27174999999999999</v>
       </c>
       <c r="S141" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="142" spans="8:19" x14ac:dyDescent="0.45">
@@ -94318,7 +94315,7 @@
         <v>0.32514999999999999</v>
       </c>
       <c r="S142" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="143" spans="8:19" x14ac:dyDescent="0.45">
@@ -94332,7 +94329,7 @@
         <v>0.37514999999999998</v>
       </c>
       <c r="S143" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="144" spans="8:19" x14ac:dyDescent="0.45">
@@ -94346,7 +94343,7 @@
         <v>0.35560000000000003</v>
       </c>
       <c r="S144" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="145" spans="16:19" x14ac:dyDescent="0.45">
@@ -94360,7 +94357,7 @@
         <v>0.3261</v>
       </c>
       <c r="S145" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="146" spans="16:19" x14ac:dyDescent="0.45">
@@ -94374,7 +94371,7 @@
         <v>0.23960000000000001</v>
       </c>
       <c r="S146" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="147" spans="16:19" x14ac:dyDescent="0.45">
@@ -94388,7 +94385,7 @@
         <v>0.1827</v>
       </c>
       <c r="S147" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="148" spans="16:19" x14ac:dyDescent="0.45">
@@ -94402,7 +94399,7 @@
         <v>0.30615000000000003</v>
       </c>
       <c r="S148" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="149" spans="16:19" x14ac:dyDescent="0.45">
@@ -94416,7 +94413,7 @@
         <v>0.39615</v>
       </c>
       <c r="S149" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="150" spans="16:19" x14ac:dyDescent="0.45">
@@ -94430,7 +94427,7 @@
         <v>0.34089999999999998</v>
       </c>
       <c r="S150" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="151" spans="16:19" x14ac:dyDescent="0.45">
@@ -94444,7 +94441,7 @@
         <v>0.37814999999999999</v>
       </c>
       <c r="S151" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="152" spans="16:19" x14ac:dyDescent="0.45">
@@ -94458,7 +94455,7 @@
         <v>0.27615000000000001</v>
       </c>
       <c r="S152" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="153" spans="16:19" x14ac:dyDescent="0.45">
@@ -94472,7 +94469,7 @@
         <v>0.16950000000000001</v>
       </c>
       <c r="S153" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="154" spans="16:19" x14ac:dyDescent="0.45">
@@ -94486,7 +94483,7 @@
         <v>0.31430000000000002</v>
       </c>
       <c r="S154" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="155" spans="16:19" x14ac:dyDescent="0.45">
@@ -94500,7 +94497,7 @@
         <v>0.40564999999999996</v>
       </c>
       <c r="S155" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="156" spans="16:19" x14ac:dyDescent="0.45">
@@ -94514,7 +94511,7 @@
         <v>0.39844999999999997</v>
       </c>
       <c r="S156" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="157" spans="16:19" x14ac:dyDescent="0.45">
@@ -94528,7 +94525,7 @@
         <v>0.38795000000000002</v>
       </c>
       <c r="S157" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="158" spans="16:19" x14ac:dyDescent="0.45">
@@ -94542,7 +94539,7 @@
         <v>0.28465000000000001</v>
       </c>
       <c r="S158" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="159" spans="16:19" x14ac:dyDescent="0.45">
@@ -94556,7 +94553,7 @@
         <v>0.2137</v>
       </c>
       <c r="S159" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="160" spans="16:19" x14ac:dyDescent="0.45">
@@ -94570,7 +94567,7 @@
         <v>0.34945000000000004</v>
       </c>
       <c r="S160" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="161" spans="16:19" x14ac:dyDescent="0.45">
@@ -94584,7 +94581,7 @@
         <v>0.33665</v>
       </c>
       <c r="S161" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="162" spans="16:19" x14ac:dyDescent="0.45">
@@ -94598,7 +94595,7 @@
         <v>0.3342</v>
       </c>
       <c r="S162" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="163" spans="16:19" x14ac:dyDescent="0.45">
@@ -94612,7 +94609,7 @@
         <v>0.35009999999999997</v>
       </c>
       <c r="S163" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="164" spans="16:19" x14ac:dyDescent="0.45">
@@ -94626,7 +94623,7 @@
         <v>0.23935000000000001</v>
       </c>
       <c r="S164" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="165" spans="16:19" x14ac:dyDescent="0.45">
@@ -94640,7 +94637,7 @@
         <v>0.17025000000000001</v>
       </c>
       <c r="S165" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="166" spans="16:19" x14ac:dyDescent="0.45">
@@ -94654,7 +94651,7 @@
         <v>0.25659999999999999</v>
       </c>
       <c r="S166" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="167" spans="16:19" x14ac:dyDescent="0.45">
@@ -94668,7 +94665,7 @@
         <v>0.31140000000000001</v>
       </c>
       <c r="S167" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="168" spans="16:19" x14ac:dyDescent="0.45">
@@ -94682,7 +94679,7 @@
         <v>0.28869999999999996</v>
       </c>
       <c r="S168" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="169" spans="16:19" x14ac:dyDescent="0.45">
@@ -94696,7 +94693,7 @@
         <v>0.29415000000000002</v>
       </c>
       <c r="S169" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="170" spans="16:19" x14ac:dyDescent="0.45">
@@ -94710,7 +94707,7 @@
         <v>0.1656</v>
       </c>
       <c r="S170" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="171" spans="16:19" x14ac:dyDescent="0.45">
@@ -94724,7 +94721,7 @@
         <v>0.19540000000000002</v>
       </c>
       <c r="S171" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="172" spans="16:19" x14ac:dyDescent="0.45">
@@ -94738,7 +94735,7 @@
         <v>0.2676</v>
       </c>
       <c r="S172" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="173" spans="16:19" x14ac:dyDescent="0.45">
@@ -94752,7 +94749,7 @@
         <v>0.27474999999999999</v>
       </c>
       <c r="S173" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="174" spans="16:19" x14ac:dyDescent="0.45">
@@ -94766,7 +94763,7 @@
         <v>0.28739999999999999</v>
       </c>
       <c r="S174" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="175" spans="16:19" x14ac:dyDescent="0.45">
@@ -94780,7 +94777,7 @@
         <v>0.32619999999999999</v>
       </c>
       <c r="S175" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="176" spans="16:19" x14ac:dyDescent="0.45">
@@ -94794,7 +94791,7 @@
         <v>0.22685</v>
       </c>
       <c r="S176" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="177" spans="16:19" x14ac:dyDescent="0.45">
@@ -94808,7 +94805,7 @@
         <v>0.1888</v>
       </c>
       <c r="S177" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="178" spans="16:19" x14ac:dyDescent="0.45">
@@ -94822,7 +94819,7 @@
         <v>0.2797</v>
       </c>
       <c r="S178" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="179" spans="16:19" x14ac:dyDescent="0.45">
@@ -94836,7 +94833,7 @@
         <v>0.31764999999999999</v>
       </c>
       <c r="S179" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="180" spans="16:19" x14ac:dyDescent="0.45">
@@ -94850,7 +94847,7 @@
         <v>0.28995000000000004</v>
       </c>
       <c r="S180" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="181" spans="16:19" x14ac:dyDescent="0.45">
@@ -94864,7 +94861,7 @@
         <v>0.31175000000000003</v>
       </c>
       <c r="S181" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="182" spans="16:19" x14ac:dyDescent="0.45">
@@ -94878,7 +94875,7 @@
         <v>0.31035000000000001</v>
       </c>
       <c r="S182" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="183" spans="16:19" x14ac:dyDescent="0.45">
@@ -94892,7 +94889,7 @@
         <v>0.187</v>
       </c>
       <c r="S183" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="184" spans="16:19" x14ac:dyDescent="0.45">
@@ -94906,7 +94903,7 @@
         <v>0.25474999999999998</v>
       </c>
       <c r="S184" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_FRA_grids_kan25/SuppXLS/Scen_TSParameters_ts_60.xlsx
+++ b/VerveStacks_FRA_grids_kan25/SuppXLS/Scen_TSParameters_ts_60.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_FRA_grids_kan25\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B58D6C58-693C-4236-9911-41EDD4932252}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC2DA712-D16A-421D-9CB8-CEE0715EDF11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28702" yWindow="-98" windowWidth="28995" windowHeight="15675" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ev_charging_uc" sheetId="6" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15148" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15149" uniqueCount="295">
   <si>
     <t>share of charging at night</t>
   </si>
@@ -903,12 +903,6 @@
     <t>S04aH08,S06aH01,S01aH08,S02aH08,S03aH08,S03aH10,S06aH08,S05aH08,S01aH10,S03aH02,S01aH09,S03aH09,S05aH09,S02aH09,S04aH09,S05aH01,S01aH02,S05aH10,S02aH01,S02aH10,S05aH02,S04aH02,S03aH01,S02aH02,S04aH10,S06aH10,S01aH01,S04aH01,S06aH02,S06aH09</t>
   </si>
   <si>
-    <t>elc_buildings</t>
-  </si>
-  <si>
-    <t>elc_industry</t>
-  </si>
-  <si>
     <t>com_pkflx</t>
   </si>
   <si>
@@ -922,6 +916,15 @@
   </si>
   <si>
     <t>hydro</t>
+  </si>
+  <si>
+    <t>*[_]buildings</t>
+  </si>
+  <si>
+    <t>*[_]industry</t>
+  </si>
+  <si>
+    <t>~TFM_INS-AT: cset_set=DEM</t>
   </si>
 </sst>
 </file>
@@ -90066,9 +90069,8 @@
         <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
         <v>~TFM_DINS-AT</v>
       </c>
-      <c r="H9" t="str">
-        <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
-        <v>~TFM_DINS-AT</v>
+      <c r="H9" t="s">
+        <v>294</v>
       </c>
       <c r="L9" t="str">
         <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
@@ -90111,19 +90113,19 @@
         <v>57</v>
       </c>
       <c r="N10" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="P10" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="Q10" t="s">
         <v>57</v>
       </c>
       <c r="R10" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="S10" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.45">
@@ -90144,7 +90146,7 @@
         <v>281</v>
       </c>
       <c r="H11" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I11" t="s">
         <v>61</v>
@@ -90171,7 +90173,7 @@
         <v>0.32884999999999998</v>
       </c>
       <c r="S11" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.45">
@@ -90188,7 +90190,7 @@
         <v>281</v>
       </c>
       <c r="H12" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I12" t="s">
         <v>63</v>
@@ -90215,7 +90217,7 @@
         <v>0.32379999999999998</v>
       </c>
       <c r="S12" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.45">
@@ -90232,7 +90234,7 @@
         <v>281</v>
       </c>
       <c r="H13" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I13" t="s">
         <v>64</v>
@@ -90259,7 +90261,7 @@
         <v>0.33195000000000002</v>
       </c>
       <c r="S13" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.45">
@@ -90276,7 +90278,7 @@
         <v>281</v>
       </c>
       <c r="H14" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I14" t="s">
         <v>65</v>
@@ -90303,7 +90305,7 @@
         <v>0.20910000000000001</v>
       </c>
       <c r="S14" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.45">
@@ -90320,7 +90322,7 @@
         <v>281</v>
       </c>
       <c r="H15" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I15" t="s">
         <v>66</v>
@@ -90347,7 +90349,7 @@
         <v>0.20760000000000001</v>
       </c>
       <c r="S15" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.45">
@@ -90364,7 +90366,7 @@
         <v>281</v>
       </c>
       <c r="H16" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I16" t="s">
         <v>67</v>
@@ -90391,7 +90393,7 @@
         <v>0.26144999999999996</v>
       </c>
       <c r="S16" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="17" spans="3:19" x14ac:dyDescent="0.45">
@@ -90408,7 +90410,7 @@
         <v>281</v>
       </c>
       <c r="H17" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I17" t="s">
         <v>68</v>
@@ -90435,7 +90437,7 @@
         <v>0.38249999999999995</v>
       </c>
       <c r="S17" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="18" spans="3:19" x14ac:dyDescent="0.45">
@@ -90452,7 +90454,7 @@
         <v>281</v>
       </c>
       <c r="H18" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I18" t="s">
         <v>69</v>
@@ -90479,7 +90481,7 @@
         <v>0.25664999999999999</v>
       </c>
       <c r="S18" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="19" spans="3:19" x14ac:dyDescent="0.45">
@@ -90496,7 +90498,7 @@
         <v>281</v>
       </c>
       <c r="H19" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I19" t="s">
         <v>70</v>
@@ -90523,7 +90525,7 @@
         <v>0.32330000000000003</v>
       </c>
       <c r="S19" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="20" spans="3:19" x14ac:dyDescent="0.45">
@@ -90540,7 +90542,7 @@
         <v>281</v>
       </c>
       <c r="H20" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I20" t="s">
         <v>71</v>
@@ -90567,7 +90569,7 @@
         <v>0.251</v>
       </c>
       <c r="S20" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="21" spans="3:19" x14ac:dyDescent="0.45">
@@ -90584,7 +90586,7 @@
         <v>281</v>
       </c>
       <c r="H21" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I21" t="s">
         <v>72</v>
@@ -90611,7 +90613,7 @@
         <v>0.16105</v>
       </c>
       <c r="S21" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="22" spans="3:19" x14ac:dyDescent="0.45">
@@ -90628,7 +90630,7 @@
         <v>281</v>
       </c>
       <c r="H22" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I22" t="s">
         <v>73</v>
@@ -90655,7 +90657,7 @@
         <v>0.21995000000000001</v>
       </c>
       <c r="S22" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="23" spans="3:19" x14ac:dyDescent="0.45">
@@ -90672,7 +90674,7 @@
         <v>281</v>
       </c>
       <c r="H23" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I23" t="s">
         <v>74</v>
@@ -90699,7 +90701,7 @@
         <v>0.25940000000000002</v>
       </c>
       <c r="S23" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="24" spans="3:19" x14ac:dyDescent="0.45">
@@ -90716,7 +90718,7 @@
         <v>281</v>
       </c>
       <c r="H24" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I24" t="s">
         <v>75</v>
@@ -90743,7 +90745,7 @@
         <v>0.23335</v>
       </c>
       <c r="S24" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="25" spans="3:19" x14ac:dyDescent="0.45">
@@ -90760,7 +90762,7 @@
         <v>281</v>
       </c>
       <c r="H25" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I25" t="s">
         <v>76</v>
@@ -90787,7 +90789,7 @@
         <v>0.22620000000000001</v>
       </c>
       <c r="S25" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="3:19" x14ac:dyDescent="0.45">
@@ -90804,7 +90806,7 @@
         <v>281</v>
       </c>
       <c r="H26" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I26" t="s">
         <v>77</v>
@@ -90831,7 +90833,7 @@
         <v>0.15055000000000002</v>
       </c>
       <c r="S26" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="3:19" x14ac:dyDescent="0.45">
@@ -90848,7 +90850,7 @@
         <v>281</v>
       </c>
       <c r="H27" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I27" t="s">
         <v>78</v>
@@ -90875,7 +90877,7 @@
         <v>0.13195000000000001</v>
       </c>
       <c r="S27" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="28" spans="3:19" x14ac:dyDescent="0.45">
@@ -90892,7 +90894,7 @@
         <v>281</v>
       </c>
       <c r="H28" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I28" t="s">
         <v>79</v>
@@ -90919,7 +90921,7 @@
         <v>0.21455000000000002</v>
       </c>
       <c r="S28" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="3:19" x14ac:dyDescent="0.45">
@@ -90936,7 +90938,7 @@
         <v>281</v>
       </c>
       <c r="H29" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I29" t="s">
         <v>80</v>
@@ -90963,7 +90965,7 @@
         <v>0.34404999999999997</v>
       </c>
       <c r="S29" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="30" spans="3:19" x14ac:dyDescent="0.45">
@@ -90980,7 +90982,7 @@
         <v>281</v>
       </c>
       <c r="H30" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I30" t="s">
         <v>81</v>
@@ -91007,7 +91009,7 @@
         <v>0.26339999999999997</v>
       </c>
       <c r="S30" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="31" spans="3:19" x14ac:dyDescent="0.45">
@@ -91024,7 +91026,7 @@
         <v>281</v>
       </c>
       <c r="H31" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I31" t="s">
         <v>82</v>
@@ -91051,7 +91053,7 @@
         <v>0.3</v>
       </c>
       <c r="S31" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="32" spans="3:19" x14ac:dyDescent="0.45">
@@ -91068,7 +91070,7 @@
         <v>281</v>
       </c>
       <c r="H32" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I32" t="s">
         <v>83</v>
@@ -91095,7 +91097,7 @@
         <v>0.192</v>
       </c>
       <c r="S32" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="33" spans="3:19" x14ac:dyDescent="0.45">
@@ -91112,7 +91114,7 @@
         <v>281</v>
       </c>
       <c r="H33" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I33" t="s">
         <v>84</v>
@@ -91139,7 +91141,7 @@
         <v>0.18359999999999999</v>
       </c>
       <c r="S33" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="34" spans="3:19" x14ac:dyDescent="0.45">
@@ -91156,7 +91158,7 @@
         <v>281</v>
       </c>
       <c r="H34" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I34" t="s">
         <v>85</v>
@@ -91183,7 +91185,7 @@
         <v>0.22505</v>
       </c>
       <c r="S34" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="35" spans="3:19" x14ac:dyDescent="0.45">
@@ -91200,7 +91202,7 @@
         <v>281</v>
       </c>
       <c r="H35" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I35" t="s">
         <v>86</v>
@@ -91227,7 +91229,7 @@
         <v>0.3337</v>
       </c>
       <c r="S35" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="36" spans="3:19" x14ac:dyDescent="0.45">
@@ -91244,7 +91246,7 @@
         <v>281</v>
       </c>
       <c r="H36" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I36" t="s">
         <v>87</v>
@@ -91271,7 +91273,7 @@
         <v>0.25495000000000001</v>
       </c>
       <c r="S36" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="37" spans="3:19" x14ac:dyDescent="0.45">
@@ -91288,7 +91290,7 @@
         <v>281</v>
       </c>
       <c r="H37" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I37" t="s">
         <v>88</v>
@@ -91315,7 +91317,7 @@
         <v>0.26024999999999998</v>
       </c>
       <c r="S37" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="38" spans="3:19" x14ac:dyDescent="0.45">
@@ -91332,7 +91334,7 @@
         <v>281</v>
       </c>
       <c r="H38" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I38" t="s">
         <v>89</v>
@@ -91359,7 +91361,7 @@
         <v>0.2064</v>
       </c>
       <c r="S38" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="39" spans="3:19" x14ac:dyDescent="0.45">
@@ -91376,7 +91378,7 @@
         <v>281</v>
       </c>
       <c r="H39" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I39" t="s">
         <v>90</v>
@@ -91403,7 +91405,7 @@
         <v>0.18104999999999999</v>
       </c>
       <c r="S39" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="40" spans="3:19" x14ac:dyDescent="0.45">
@@ -91420,7 +91422,7 @@
         <v>281</v>
       </c>
       <c r="H40" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I40" t="s">
         <v>91</v>
@@ -91447,7 +91449,7 @@
         <v>0.23249999999999998</v>
       </c>
       <c r="S40" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="41" spans="3:19" x14ac:dyDescent="0.45">
@@ -91464,7 +91466,7 @@
         <v>281</v>
       </c>
       <c r="H41" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I41" t="s">
         <v>92</v>
@@ -91491,7 +91493,7 @@
         <v>0.32094999999999996</v>
       </c>
       <c r="S41" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="42" spans="3:19" x14ac:dyDescent="0.45">
@@ -91508,7 +91510,7 @@
         <v>281</v>
       </c>
       <c r="H42" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I42" t="s">
         <v>93</v>
@@ -91535,7 +91537,7 @@
         <v>0.33640000000000003</v>
       </c>
       <c r="S42" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="43" spans="3:19" x14ac:dyDescent="0.45">
@@ -91552,7 +91554,7 @@
         <v>281</v>
       </c>
       <c r="H43" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I43" t="s">
         <v>94</v>
@@ -91579,7 +91581,7 @@
         <v>0.3276</v>
       </c>
       <c r="S43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="44" spans="3:19" x14ac:dyDescent="0.45">
@@ -91596,7 +91598,7 @@
         <v>281</v>
       </c>
       <c r="H44" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I44" t="s">
         <v>95</v>
@@ -91623,7 +91625,7 @@
         <v>0.18459999999999999</v>
       </c>
       <c r="S44" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="45" spans="3:19" x14ac:dyDescent="0.45">
@@ -91640,7 +91642,7 @@
         <v>281</v>
       </c>
       <c r="H45" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I45" t="s">
         <v>96</v>
@@ -91667,7 +91669,7 @@
         <v>0.20365</v>
       </c>
       <c r="S45" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="46" spans="3:19" x14ac:dyDescent="0.45">
@@ -91684,7 +91686,7 @@
         <v>281</v>
       </c>
       <c r="H46" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I46" t="s">
         <v>97</v>
@@ -91711,7 +91713,7 @@
         <v>0.23815000000000003</v>
       </c>
       <c r="S46" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="47" spans="3:19" x14ac:dyDescent="0.45">
@@ -91728,7 +91730,7 @@
         <v>281</v>
       </c>
       <c r="H47" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I47" t="s">
         <v>98</v>
@@ -91755,7 +91757,7 @@
         <v>0.3876</v>
       </c>
       <c r="S47" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="48" spans="3:19" x14ac:dyDescent="0.45">
@@ -91772,7 +91774,7 @@
         <v>281</v>
       </c>
       <c r="H48" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I48" t="s">
         <v>99</v>
@@ -91799,7 +91801,7 @@
         <v>0.33899999999999997</v>
       </c>
       <c r="S48" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="49" spans="3:19" x14ac:dyDescent="0.45">
@@ -91816,7 +91818,7 @@
         <v>281</v>
       </c>
       <c r="H49" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I49" t="s">
         <v>100</v>
@@ -91843,7 +91845,7 @@
         <v>0.35389999999999999</v>
       </c>
       <c r="S49" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="50" spans="3:19" x14ac:dyDescent="0.45">
@@ -91860,7 +91862,7 @@
         <v>281</v>
       </c>
       <c r="H50" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I50" t="s">
         <v>101</v>
@@ -91887,7 +91889,7 @@
         <v>0.21375</v>
       </c>
       <c r="S50" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="51" spans="3:19" x14ac:dyDescent="0.45">
@@ -91904,7 +91906,7 @@
         <v>281</v>
       </c>
       <c r="H51" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I51" t="s">
         <v>102</v>
@@ -91931,7 +91933,7 @@
         <v>0.18010000000000001</v>
       </c>
       <c r="S51" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="52" spans="3:19" x14ac:dyDescent="0.45">
@@ -91948,7 +91950,7 @@
         <v>281</v>
       </c>
       <c r="H52" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I52" t="s">
         <v>103</v>
@@ -91975,7 +91977,7 @@
         <v>0.26650000000000001</v>
       </c>
       <c r="S52" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="53" spans="3:19" x14ac:dyDescent="0.45">
@@ -91992,7 +91994,7 @@
         <v>281</v>
       </c>
       <c r="H53" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I53" t="s">
         <v>104</v>
@@ -92019,7 +92021,7 @@
         <v>0.34970000000000001</v>
       </c>
       <c r="S53" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="54" spans="3:19" x14ac:dyDescent="0.45">
@@ -92036,7 +92038,7 @@
         <v>281</v>
       </c>
       <c r="H54" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I54" t="s">
         <v>105</v>
@@ -92063,7 +92065,7 @@
         <v>0.32765</v>
       </c>
       <c r="S54" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="55" spans="3:19" x14ac:dyDescent="0.45">
@@ -92080,7 +92082,7 @@
         <v>281</v>
       </c>
       <c r="H55" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I55" t="s">
         <v>106</v>
@@ -92107,7 +92109,7 @@
         <v>0.36409999999999998</v>
       </c>
       <c r="S55" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="56" spans="3:19" x14ac:dyDescent="0.45">
@@ -92124,7 +92126,7 @@
         <v>281</v>
       </c>
       <c r="H56" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I56" t="s">
         <v>107</v>
@@ -92151,7 +92153,7 @@
         <v>0.19919999999999999</v>
       </c>
       <c r="S56" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="57" spans="3:19" x14ac:dyDescent="0.45">
@@ -92168,7 +92170,7 @@
         <v>281</v>
       </c>
       <c r="H57" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I57" t="s">
         <v>108</v>
@@ -92195,7 +92197,7 @@
         <v>0.1653</v>
       </c>
       <c r="S57" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="58" spans="3:19" x14ac:dyDescent="0.45">
@@ -92212,7 +92214,7 @@
         <v>281</v>
       </c>
       <c r="H58" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I58" t="s">
         <v>109</v>
@@ -92239,7 +92241,7 @@
         <v>0.21804999999999999</v>
       </c>
       <c r="S58" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="59" spans="3:19" x14ac:dyDescent="0.45">
@@ -92256,7 +92258,7 @@
         <v>281</v>
       </c>
       <c r="H59" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I59" t="s">
         <v>110</v>
@@ -92283,7 +92285,7 @@
         <v>0.30020000000000002</v>
       </c>
       <c r="S59" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="60" spans="3:19" x14ac:dyDescent="0.45">
@@ -92300,7 +92302,7 @@
         <v>281</v>
       </c>
       <c r="H60" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I60" t="s">
         <v>111</v>
@@ -92327,7 +92329,7 @@
         <v>0.34819999999999995</v>
       </c>
       <c r="S60" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="61" spans="3:19" x14ac:dyDescent="0.45">
@@ -92344,7 +92346,7 @@
         <v>281</v>
       </c>
       <c r="H61" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I61" t="s">
         <v>112</v>
@@ -92371,7 +92373,7 @@
         <v>0.36664999999999998</v>
       </c>
       <c r="S61" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="62" spans="3:19" x14ac:dyDescent="0.45">
@@ -92388,7 +92390,7 @@
         <v>281</v>
       </c>
       <c r="H62" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I62" t="s">
         <v>113</v>
@@ -92415,7 +92417,7 @@
         <v>0.2026</v>
       </c>
       <c r="S62" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="63" spans="3:19" x14ac:dyDescent="0.45">
@@ -92432,7 +92434,7 @@
         <v>281</v>
       </c>
       <c r="H63" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I63" t="s">
         <v>114</v>
@@ -92459,7 +92461,7 @@
         <v>0.18235000000000001</v>
       </c>
       <c r="S63" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="64" spans="3:19" x14ac:dyDescent="0.45">
@@ -92476,7 +92478,7 @@
         <v>281</v>
       </c>
       <c r="H64" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I64" t="s">
         <v>115</v>
@@ -92503,7 +92505,7 @@
         <v>0.29704999999999998</v>
       </c>
       <c r="S64" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="65" spans="3:19" x14ac:dyDescent="0.45">
@@ -92520,7 +92522,7 @@
         <v>281</v>
       </c>
       <c r="H65" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I65" t="s">
         <v>116</v>
@@ -92547,7 +92549,7 @@
         <v>0.33479999999999999</v>
       </c>
       <c r="S65" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="66" spans="3:19" x14ac:dyDescent="0.45">
@@ -92564,7 +92566,7 @@
         <v>281</v>
       </c>
       <c r="H66" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I66" t="s">
         <v>117</v>
@@ -92591,7 +92593,7 @@
         <v>0.33210000000000001</v>
       </c>
       <c r="S66" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="67" spans="3:19" x14ac:dyDescent="0.45">
@@ -92608,7 +92610,7 @@
         <v>281</v>
       </c>
       <c r="H67" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I67" t="s">
         <v>118</v>
@@ -92635,7 +92637,7 @@
         <v>0.34714999999999996</v>
       </c>
       <c r="S67" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="68" spans="3:19" x14ac:dyDescent="0.45">
@@ -92652,7 +92654,7 @@
         <v>281</v>
       </c>
       <c r="H68" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I68" t="s">
         <v>119</v>
@@ -92679,7 +92681,7 @@
         <v>0.24829999999999999</v>
       </c>
       <c r="S68" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="69" spans="3:19" x14ac:dyDescent="0.45">
@@ -92696,7 +92698,7 @@
         <v>281</v>
       </c>
       <c r="H69" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I69" t="s">
         <v>120</v>
@@ -92723,7 +92725,7 @@
         <v>0.17255000000000001</v>
       </c>
       <c r="S69" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="70" spans="3:19" x14ac:dyDescent="0.45">
@@ -92740,7 +92742,7 @@
         <v>281</v>
       </c>
       <c r="H70" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I70" t="s">
         <v>121</v>
@@ -92767,12 +92769,12 @@
         <v>0.29925000000000002</v>
       </c>
       <c r="S70" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="71" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H71" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I71" t="s">
         <v>61</v>
@@ -92790,12 +92792,12 @@
         <v>0.30010000000000003</v>
       </c>
       <c r="S71" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="72" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H72" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I72" t="s">
         <v>63</v>
@@ -92813,12 +92815,12 @@
         <v>0.23294999999999999</v>
       </c>
       <c r="S72" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="73" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H73" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I73" t="s">
         <v>64</v>
@@ -92836,12 +92838,12 @@
         <v>0.28615000000000002</v>
       </c>
       <c r="S73" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="74" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H74" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I74" t="s">
         <v>65</v>
@@ -92859,12 +92861,12 @@
         <v>0.20265</v>
       </c>
       <c r="S74" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="75" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H75" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I75" t="s">
         <v>66</v>
@@ -92882,12 +92884,12 @@
         <v>0.152</v>
       </c>
       <c r="S75" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="76" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H76" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I76" t="s">
         <v>67</v>
@@ -92905,12 +92907,12 @@
         <v>0.24084999999999998</v>
       </c>
       <c r="S76" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="77" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H77" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I77" t="s">
         <v>68</v>
@@ -92928,12 +92930,12 @@
         <v>0.30495</v>
       </c>
       <c r="S77" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="78" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H78" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I78" t="s">
         <v>69</v>
@@ -92951,12 +92953,12 @@
         <v>0.33194999999999997</v>
       </c>
       <c r="S78" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="79" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H79" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I79" t="s">
         <v>70</v>
@@ -92974,12 +92976,12 @@
         <v>0.31174999999999997</v>
       </c>
       <c r="S79" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="80" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H80" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I80" t="s">
         <v>71</v>
@@ -92997,12 +92999,12 @@
         <v>0.24269999999999997</v>
       </c>
       <c r="S80" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="81" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H81" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I81" t="s">
         <v>72</v>
@@ -93020,12 +93022,12 @@
         <v>0.1401</v>
       </c>
       <c r="S81" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="82" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H82" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I82" t="s">
         <v>73</v>
@@ -93043,12 +93045,12 @@
         <v>0.26954999999999996</v>
       </c>
       <c r="S82" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="83" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H83" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I83" t="s">
         <v>74</v>
@@ -93066,12 +93068,12 @@
         <v>0.2893</v>
       </c>
       <c r="S83" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="84" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H84" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I84" t="s">
         <v>75</v>
@@ -93089,12 +93091,12 @@
         <v>0.25214999999999999</v>
       </c>
       <c r="S84" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="85" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H85" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I85" t="s">
         <v>76</v>
@@ -93112,12 +93114,12 @@
         <v>0.28079999999999999</v>
       </c>
       <c r="S85" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="86" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H86" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I86" t="s">
         <v>77</v>
@@ -93135,12 +93137,12 @@
         <v>0.2311</v>
       </c>
       <c r="S86" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="87" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H87" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I87" t="s">
         <v>78</v>
@@ -93158,12 +93160,12 @@
         <v>0.10925</v>
       </c>
       <c r="S87" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="88" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H88" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I88" t="s">
         <v>79</v>
@@ -93181,12 +93183,12 @@
         <v>0.24104999999999999</v>
       </c>
       <c r="S88" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="89" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H89" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I89" t="s">
         <v>80</v>
@@ -93204,12 +93206,12 @@
         <v>0.30325000000000002</v>
       </c>
       <c r="S89" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="90" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H90" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I90" t="s">
         <v>81</v>
@@ -93227,12 +93229,12 @@
         <v>0.34694999999999998</v>
       </c>
       <c r="S90" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="91" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H91" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I91" t="s">
         <v>82</v>
@@ -93250,12 +93252,12 @@
         <v>0.30105000000000004</v>
       </c>
       <c r="S91" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="92" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H92" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I92" t="s">
         <v>83</v>
@@ -93273,12 +93275,12 @@
         <v>0.23320000000000002</v>
       </c>
       <c r="S92" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="93" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H93" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I93" t="s">
         <v>84</v>
@@ -93296,12 +93298,12 @@
         <v>0.16464999999999999</v>
       </c>
       <c r="S93" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="94" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H94" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I94" t="s">
         <v>85</v>
@@ -93319,12 +93321,12 @@
         <v>0.2283</v>
       </c>
       <c r="S94" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="95" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H95" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I95" t="s">
         <v>86</v>
@@ -93342,12 +93344,12 @@
         <v>0.30945</v>
       </c>
       <c r="S95" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="96" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H96" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I96" t="s">
         <v>87</v>
@@ -93365,12 +93367,12 @@
         <v>0.30315000000000003</v>
       </c>
       <c r="S96" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="97" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H97" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I97" t="s">
         <v>88</v>
@@ -93388,12 +93390,12 @@
         <v>0.32484999999999997</v>
       </c>
       <c r="S97" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="98" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H98" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I98" t="s">
         <v>89</v>
@@ -93411,12 +93413,12 @@
         <v>0.18835000000000002</v>
       </c>
       <c r="S98" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="99" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H99" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I99" t="s">
         <v>90</v>
@@ -93434,12 +93436,12 @@
         <v>0.16310000000000002</v>
       </c>
       <c r="S99" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="100" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H100" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I100" t="s">
         <v>91</v>
@@ -93457,12 +93459,12 @@
         <v>0.2392</v>
       </c>
       <c r="S100" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="101" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H101" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I101" t="s">
         <v>92</v>
@@ -93480,12 +93482,12 @@
         <v>0.2792</v>
       </c>
       <c r="S101" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="102" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H102" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I102" t="s">
         <v>93</v>
@@ -93503,12 +93505,12 @@
         <v>0.25224999999999997</v>
       </c>
       <c r="S102" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="103" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H103" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I103" t="s">
         <v>94</v>
@@ -93526,12 +93528,12 @@
         <v>0.28939999999999999</v>
       </c>
       <c r="S103" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="104" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H104" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I104" t="s">
         <v>95</v>
@@ -93549,12 +93551,12 @@
         <v>0.16775000000000001</v>
       </c>
       <c r="S104" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="105" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H105" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I105" t="s">
         <v>96</v>
@@ -93572,12 +93574,12 @@
         <v>0.14505000000000001</v>
       </c>
       <c r="S105" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="106" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H106" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I106" t="s">
         <v>97</v>
@@ -93595,12 +93597,12 @@
         <v>0.24359999999999998</v>
       </c>
       <c r="S106" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="107" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H107" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I107" t="s">
         <v>98</v>
@@ -93618,12 +93620,12 @@
         <v>0.35544999999999999</v>
       </c>
       <c r="S107" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="108" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H108" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I108" t="s">
         <v>99</v>
@@ -93641,12 +93643,12 @@
         <v>0.28994999999999999</v>
       </c>
       <c r="S108" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="109" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H109" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I109" t="s">
         <v>100</v>
@@ -93664,12 +93666,12 @@
         <v>0.31855</v>
       </c>
       <c r="S109" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="110" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H110" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I110" t="s">
         <v>101</v>
@@ -93687,12 +93689,12 @@
         <v>0.183</v>
       </c>
       <c r="S110" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="111" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H111" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I111" t="s">
         <v>102</v>
@@ -93710,12 +93712,12 @@
         <v>0.13450000000000001</v>
       </c>
       <c r="S111" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="112" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H112" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I112" t="s">
         <v>103</v>
@@ -93733,12 +93735,12 @@
         <v>0.25585000000000002</v>
       </c>
       <c r="S112" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="113" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H113" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I113" t="s">
         <v>104</v>
@@ -93756,12 +93758,12 @@
         <v>0.37395</v>
       </c>
       <c r="S113" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="114" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H114" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I114" t="s">
         <v>105</v>
@@ -93779,12 +93781,12 @@
         <v>0.28594999999999998</v>
       </c>
       <c r="S114" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="115" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H115" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I115" t="s">
         <v>106</v>
@@ -93802,12 +93804,12 @@
         <v>0.32190000000000002</v>
       </c>
       <c r="S115" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="116" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H116" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I116" t="s">
         <v>107</v>
@@ -93825,12 +93827,12 @@
         <v>0.21550000000000002</v>
       </c>
       <c r="S116" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="117" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H117" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I117" t="s">
         <v>108</v>
@@ -93848,12 +93850,12 @@
         <v>0.19924999999999998</v>
       </c>
       <c r="S117" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="118" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H118" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I118" t="s">
         <v>109</v>
@@ -93871,12 +93873,12 @@
         <v>0.28159999999999996</v>
       </c>
       <c r="S118" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="119" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H119" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I119" t="s">
         <v>110</v>
@@ -93894,12 +93896,12 @@
         <v>0.41005000000000003</v>
       </c>
       <c r="S119" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="120" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H120" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I120" t="s">
         <v>111</v>
@@ -93917,12 +93919,12 @@
         <v>0.34389999999999998</v>
       </c>
       <c r="S120" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="121" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H121" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I121" t="s">
         <v>112</v>
@@ -93940,12 +93942,12 @@
         <v>0.39655000000000001</v>
       </c>
       <c r="S121" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="122" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H122" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I122" t="s">
         <v>113</v>
@@ -93963,12 +93965,12 @@
         <v>0.24129999999999999</v>
       </c>
       <c r="S122" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="123" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H123" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I123" t="s">
         <v>114</v>
@@ -93986,12 +93988,12 @@
         <v>0.2127</v>
       </c>
       <c r="S123" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="124" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H124" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I124" t="s">
         <v>115</v>
@@ -94009,12 +94011,12 @@
         <v>0.30910000000000004</v>
       </c>
       <c r="S124" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="125" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H125" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I125" t="s">
         <v>116</v>
@@ -94032,12 +94034,12 @@
         <v>0.37570000000000003</v>
       </c>
       <c r="S125" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="126" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H126" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I126" t="s">
         <v>117</v>
@@ -94055,12 +94057,12 @@
         <v>0.36940000000000001</v>
       </c>
       <c r="S126" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="127" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H127" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I127" t="s">
         <v>118</v>
@@ -94078,12 +94080,12 @@
         <v>0.33594999999999997</v>
       </c>
       <c r="S127" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="128" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H128" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I128" t="s">
         <v>119</v>
@@ -94101,12 +94103,12 @@
         <v>0.2392</v>
       </c>
       <c r="S128" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="129" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H129" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I129" t="s">
         <v>120</v>
@@ -94124,12 +94126,12 @@
         <v>0.24365000000000001</v>
       </c>
       <c r="S129" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="130" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H130" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I130" t="s">
         <v>121</v>
@@ -94147,7 +94149,7 @@
         <v>0.37475000000000003</v>
       </c>
       <c r="S130" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="131" spans="8:19" x14ac:dyDescent="0.45">
@@ -94161,7 +94163,7 @@
         <v>0.40375</v>
       </c>
       <c r="S131" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="132" spans="8:19" x14ac:dyDescent="0.45">
@@ -94175,7 +94177,7 @@
         <v>0.38624999999999998</v>
       </c>
       <c r="S132" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="133" spans="8:19" x14ac:dyDescent="0.45">
@@ -94189,7 +94191,7 @@
         <v>0.41835</v>
       </c>
       <c r="S133" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="134" spans="8:19" x14ac:dyDescent="0.45">
@@ -94203,7 +94205,7 @@
         <v>0.27644999999999997</v>
       </c>
       <c r="S134" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="135" spans="8:19" x14ac:dyDescent="0.45">
@@ -94217,7 +94219,7 @@
         <v>0.22705</v>
       </c>
       <c r="S135" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="136" spans="8:19" x14ac:dyDescent="0.45">
@@ -94231,7 +94233,7 @@
         <v>0.34904999999999997</v>
       </c>
       <c r="S136" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="137" spans="8:19" x14ac:dyDescent="0.45">
@@ -94245,7 +94247,7 @@
         <v>0.36795</v>
       </c>
       <c r="S137" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="138" spans="8:19" x14ac:dyDescent="0.45">
@@ -94259,7 +94261,7 @@
         <v>0.34635000000000005</v>
       </c>
       <c r="S138" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="139" spans="8:19" x14ac:dyDescent="0.45">
@@ -94273,7 +94275,7 @@
         <v>0.33884999999999998</v>
       </c>
       <c r="S139" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="140" spans="8:19" x14ac:dyDescent="0.45">
@@ -94287,7 +94289,7 @@
         <v>0.21560000000000001</v>
       </c>
       <c r="S140" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="141" spans="8:19" x14ac:dyDescent="0.45">
@@ -94301,7 +94303,7 @@
         <v>0.27174999999999999</v>
       </c>
       <c r="S141" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="142" spans="8:19" x14ac:dyDescent="0.45">
@@ -94315,7 +94317,7 @@
         <v>0.32514999999999999</v>
       </c>
       <c r="S142" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="143" spans="8:19" x14ac:dyDescent="0.45">
@@ -94329,7 +94331,7 @@
         <v>0.37514999999999998</v>
       </c>
       <c r="S143" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="144" spans="8:19" x14ac:dyDescent="0.45">
@@ -94343,7 +94345,7 @@
         <v>0.35560000000000003</v>
       </c>
       <c r="S144" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="145" spans="16:19" x14ac:dyDescent="0.45">
@@ -94357,7 +94359,7 @@
         <v>0.3261</v>
       </c>
       <c r="S145" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="146" spans="16:19" x14ac:dyDescent="0.45">
@@ -94371,7 +94373,7 @@
         <v>0.23960000000000001</v>
       </c>
       <c r="S146" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="147" spans="16:19" x14ac:dyDescent="0.45">
@@ -94385,7 +94387,7 @@
         <v>0.1827</v>
       </c>
       <c r="S147" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="148" spans="16:19" x14ac:dyDescent="0.45">
@@ -94399,7 +94401,7 @@
         <v>0.30615000000000003</v>
       </c>
       <c r="S148" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="149" spans="16:19" x14ac:dyDescent="0.45">
@@ -94413,7 +94415,7 @@
         <v>0.39615</v>
       </c>
       <c r="S149" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="150" spans="16:19" x14ac:dyDescent="0.45">
@@ -94427,7 +94429,7 @@
         <v>0.34089999999999998</v>
       </c>
       <c r="S150" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="151" spans="16:19" x14ac:dyDescent="0.45">
@@ -94441,7 +94443,7 @@
         <v>0.37814999999999999</v>
       </c>
       <c r="S151" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="152" spans="16:19" x14ac:dyDescent="0.45">
@@ -94455,7 +94457,7 @@
         <v>0.27615000000000001</v>
       </c>
       <c r="S152" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="153" spans="16:19" x14ac:dyDescent="0.45">
@@ -94469,7 +94471,7 @@
         <v>0.16950000000000001</v>
       </c>
       <c r="S153" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="154" spans="16:19" x14ac:dyDescent="0.45">
@@ -94483,7 +94485,7 @@
         <v>0.31430000000000002</v>
       </c>
       <c r="S154" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="155" spans="16:19" x14ac:dyDescent="0.45">
@@ -94497,7 +94499,7 @@
         <v>0.40564999999999996</v>
       </c>
       <c r="S155" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="156" spans="16:19" x14ac:dyDescent="0.45">
@@ -94511,7 +94513,7 @@
         <v>0.39844999999999997</v>
       </c>
       <c r="S156" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="157" spans="16:19" x14ac:dyDescent="0.45">
@@ -94525,7 +94527,7 @@
         <v>0.38795000000000002</v>
       </c>
       <c r="S157" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="158" spans="16:19" x14ac:dyDescent="0.45">
@@ -94539,7 +94541,7 @@
         <v>0.28465000000000001</v>
       </c>
       <c r="S158" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="159" spans="16:19" x14ac:dyDescent="0.45">
@@ -94553,7 +94555,7 @@
         <v>0.2137</v>
       </c>
       <c r="S159" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="160" spans="16:19" x14ac:dyDescent="0.45">
@@ -94567,7 +94569,7 @@
         <v>0.34945000000000004</v>
       </c>
       <c r="S160" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="161" spans="16:19" x14ac:dyDescent="0.45">
@@ -94581,7 +94583,7 @@
         <v>0.33665</v>
       </c>
       <c r="S161" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="162" spans="16:19" x14ac:dyDescent="0.45">
@@ -94595,7 +94597,7 @@
         <v>0.3342</v>
       </c>
       <c r="S162" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="163" spans="16:19" x14ac:dyDescent="0.45">
@@ -94609,7 +94611,7 @@
         <v>0.35009999999999997</v>
       </c>
       <c r="S163" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="164" spans="16:19" x14ac:dyDescent="0.45">
@@ -94623,7 +94625,7 @@
         <v>0.23935000000000001</v>
       </c>
       <c r="S164" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="165" spans="16:19" x14ac:dyDescent="0.45">
@@ -94637,7 +94639,7 @@
         <v>0.17025000000000001</v>
       </c>
       <c r="S165" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="166" spans="16:19" x14ac:dyDescent="0.45">
@@ -94651,7 +94653,7 @@
         <v>0.25659999999999999</v>
       </c>
       <c r="S166" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="167" spans="16:19" x14ac:dyDescent="0.45">
@@ -94665,7 +94667,7 @@
         <v>0.31140000000000001</v>
       </c>
       <c r="S167" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="168" spans="16:19" x14ac:dyDescent="0.45">
@@ -94679,7 +94681,7 @@
         <v>0.28869999999999996</v>
       </c>
       <c r="S168" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="169" spans="16:19" x14ac:dyDescent="0.45">
@@ -94693,7 +94695,7 @@
         <v>0.29415000000000002</v>
       </c>
       <c r="S169" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="170" spans="16:19" x14ac:dyDescent="0.45">
@@ -94707,7 +94709,7 @@
         <v>0.1656</v>
       </c>
       <c r="S170" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="171" spans="16:19" x14ac:dyDescent="0.45">
@@ -94721,7 +94723,7 @@
         <v>0.19540000000000002</v>
       </c>
       <c r="S171" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="172" spans="16:19" x14ac:dyDescent="0.45">
@@ -94735,7 +94737,7 @@
         <v>0.2676</v>
       </c>
       <c r="S172" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="173" spans="16:19" x14ac:dyDescent="0.45">
@@ -94749,7 +94751,7 @@
         <v>0.27474999999999999</v>
       </c>
       <c r="S173" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="174" spans="16:19" x14ac:dyDescent="0.45">
@@ -94763,7 +94765,7 @@
         <v>0.28739999999999999</v>
       </c>
       <c r="S174" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="175" spans="16:19" x14ac:dyDescent="0.45">
@@ -94777,7 +94779,7 @@
         <v>0.32619999999999999</v>
       </c>
       <c r="S175" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="176" spans="16:19" x14ac:dyDescent="0.45">
@@ -94791,7 +94793,7 @@
         <v>0.22685</v>
       </c>
       <c r="S176" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="177" spans="16:19" x14ac:dyDescent="0.45">
@@ -94805,7 +94807,7 @@
         <v>0.1888</v>
       </c>
       <c r="S177" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="178" spans="16:19" x14ac:dyDescent="0.45">
@@ -94819,7 +94821,7 @@
         <v>0.2797</v>
       </c>
       <c r="S178" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="179" spans="16:19" x14ac:dyDescent="0.45">
@@ -94833,7 +94835,7 @@
         <v>0.31764999999999999</v>
       </c>
       <c r="S179" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="180" spans="16:19" x14ac:dyDescent="0.45">
@@ -94847,7 +94849,7 @@
         <v>0.28995000000000004</v>
       </c>
       <c r="S180" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="181" spans="16:19" x14ac:dyDescent="0.45">
@@ -94861,7 +94863,7 @@
         <v>0.31175000000000003</v>
       </c>
       <c r="S181" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="182" spans="16:19" x14ac:dyDescent="0.45">
@@ -94875,7 +94877,7 @@
         <v>0.31035000000000001</v>
       </c>
       <c r="S182" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="183" spans="16:19" x14ac:dyDescent="0.45">
@@ -94889,7 +94891,7 @@
         <v>0.187</v>
       </c>
       <c r="S183" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="184" spans="16:19" x14ac:dyDescent="0.45">
@@ -94903,7 +94905,7 @@
         <v>0.25474999999999998</v>
       </c>
       <c r="S184" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
   </sheetData>
